--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,13 @@
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -152,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -167,6 +174,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -199,7 +209,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,7 +221,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -685,7 +695,7 @@
           <t>ClinicalTrials.gov NCT03529110</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>DESTINY-Breast03 primary analysis cutoff</t>
         </is>
@@ -727,7 +737,7 @@
           <t>ESMO 2021 presentation</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>First presentation at ESMO Congress 2021</t>
         </is>
@@ -765,7 +775,7 @@
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Full approval for 2L+ HER2+ mBC based on DESTINY-Breast03</t>
         </is>
@@ -804,10 +814,10 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>EMA centralized procedure; EC marketing authorization</t>
         </is>
@@ -846,10 +856,10 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Same EMA approval applies to all EU5</t>
         </is>
@@ -888,10 +898,10 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -926,10 +936,10 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -967,7 +977,7 @@
           <t>MHRA GBR reliance procedure</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>MHRA followed EMA timeline via reliance pathway</t>
         </is>
@@ -1009,7 +1019,7 @@
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1027,7 +1037,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sep 2022</t>
         </is>
@@ -1047,7 +1057,7 @@
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Category 1 preferred within ~1 month of FDA approval</t>
         </is>
@@ -1069,7 +1079,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Sep 2022</t>
         </is>
@@ -1089,7 +1099,7 @@
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -1111,7 +1121,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1131,7 +1141,7 @@
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Updated recommendation following full publication</t>
         </is>
@@ -1153,7 +1163,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1173,7 +1183,7 @@
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1191,7 +1201,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1211,7 +1221,7 @@
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1229,7 +1239,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1249,7 +1259,7 @@
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1267,7 +1277,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1287,7 +1297,7 @@
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1325,7 +1335,7 @@
           <t>NICE TA942</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Recommended for routine commissioning</t>
         </is>
@@ -1347,7 +1357,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>May 2023</t>
         </is>
@@ -1367,7 +1377,7 @@
           <t>G-BA AMNOG assessment</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact G-BA decision date needs verification. Considerable additional benefit; approximate date.</t>
         </is>
@@ -1389,7 +1399,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
@@ -1409,7 +1419,7 @@
           <t>Estimated from typical HAS timeline</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact HAS Transparency Committee opinion date needs research</t>
         </is>
@@ -1431,7 +1441,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
@@ -1451,7 +1461,7 @@
           <t>Estimated from typical AIFA timeline</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact AIFA Gazzetta Ufficiale publication date needs research</t>
         </is>
@@ -1473,7 +1483,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Apr 2024</t>
         </is>
@@ -1493,7 +1503,7 @@
           <t>Estimated from typical AEMPS/IPT timeline</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact Spanish pricing/reimbursement date needs research</t>
         </is>
@@ -1515,7 +1525,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Jun 2023</t>
         </is>
@@ -1535,7 +1545,7 @@
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Recommended for reimbursement with clinical criteria</t>
         </is>
@@ -1557,7 +1567,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Aug 2022</t>
         </is>
@@ -1577,7 +1587,7 @@
           <t>Daiichi Sankyo press release</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>US commercial launch within days of FDA approval</t>
         </is>
@@ -1599,7 +1609,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -1609,6 +1619,31 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1704,7 +1739,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Nov 2020</t>
         </is>
@@ -1724,7 +1759,7 @@
           <t>ClinicalTrials.gov NCT02574455</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>ASCENT trial primary completion</t>
         </is>
@@ -1763,10 +1798,10 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ESMO 2020 presentation</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+          <t>ESMO 2020 — NEJM publication</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Primary results presented at ESMO Virtual 2020</t>
         </is>
@@ -1804,7 +1839,7 @@
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Regular approval for 3L+ mTNBC (accelerated approval Apr 2020 converted)</t>
         </is>
@@ -1843,10 +1878,10 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>EMA centralized procedure; ~7 months post-FDA</t>
         </is>
@@ -1885,10 +1920,10 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1923,10 +1958,10 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1961,10 +1996,10 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>EC decision</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+          <t>EC decision — EMA EPAR</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1982,7 +2017,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Dec 2021</t>
         </is>
@@ -2002,7 +2037,7 @@
           <t>MHRA approval</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>MHRA followed shortly after EMA; approximate date</t>
         </is>
@@ -2044,7 +2079,7 @@
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>~15 months post-FDA</t>
         </is>
@@ -2066,7 +2101,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>May 2021</t>
         </is>
@@ -2086,7 +2121,7 @@
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Added within one update cycle of full approval</t>
         </is>
@@ -2108,7 +2143,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>May 2021</t>
         </is>
@@ -2128,7 +2163,7 @@
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2146,7 +2181,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2166,7 +2201,7 @@
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Approximate timing of ESMO guideline inclusion</t>
         </is>
@@ -2188,7 +2223,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2208,7 +2243,7 @@
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2226,7 +2261,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2246,7 +2281,7 @@
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2264,7 +2299,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2284,7 +2319,7 @@
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2302,7 +2337,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2322,7 +2357,7 @@
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2360,7 +2395,7 @@
           <t>NICE TA900</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Recommended via Cancer Drugs Fund; ~27 months post-FDA</t>
         </is>
@@ -2382,7 +2417,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Apr 2022</t>
         </is>
@@ -2402,7 +2437,7 @@
           <t>G-BA AMNOG assessment</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact date approximate — verify against G-BA records</t>
         </is>
@@ -2424,7 +2459,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Sep 2022</t>
         </is>
@@ -2444,7 +2479,7 @@
           <t>Estimated from typical HAS timeline</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact HAS TC opinion date for Trodelvy 3L+ needs research</t>
         </is>
@@ -2466,7 +2501,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Mar 2023</t>
         </is>
@@ -2486,7 +2521,7 @@
           <t>Estimated from typical AIFA timeline</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact AIFA GU publication date needs research</t>
         </is>
@@ -2508,7 +2543,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Jul 2023</t>
         </is>
@@ -2528,7 +2563,7 @@
           <t>Estimated from typical AEMPS timeline</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact Spanish pricing decision date needs research</t>
         </is>
@@ -2550,7 +2585,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Oct 2022</t>
         </is>
@@ -2570,7 +2605,7 @@
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Approximate date; ~18 months post-FDA</t>
         </is>
@@ -2592,7 +2627,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Apr 2021</t>
         </is>
@@ -2612,7 +2647,7 @@
           <t>Gilead press release</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>US launch shortly after FDA approval</t>
         </is>
@@ -2634,7 +2669,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2644,6 +2679,31 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2727,32 +2787,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2765,32 +2825,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F5" s="13" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2803,32 +2863,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2841,32 +2901,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F7" s="13" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2879,32 +2939,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2917,32 +2977,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2955,32 +3015,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2993,32 +3053,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3031,32 +3091,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3069,32 +3129,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3107,32 +3167,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3145,32 +3205,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3183,32 +3243,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3221,32 +3281,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3259,32 +3319,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>11.8</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>11.8</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3297,32 +3357,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>13.9</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>16.8</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3335,32 +3395,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3373,32 +3433,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3411,32 +3471,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3449,32 +3509,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3534,7 +3594,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -3544,7 +3604,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -3581,22 +3641,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3606,7 +3666,7 @@
           <t>ClinicalTrials.gov NCT05382286 (estimated)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>ASCENT-03 estimated primary completion; verify on ClinicalTrials.gov</t>
         </is>
@@ -3628,32 +3688,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Estimated based on typical PCD-to-readout lag</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Gilead targeting data for H2 2025 / H1 2026</t>
         </is>
@@ -3675,22 +3735,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3700,7 +3760,7 @@
           <t>Gilead guidance: accelerated 1L launch H2 2026</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Assumes standard sBLA review (~6-8 months) or Priority Review (~6 months)</t>
         </is>
@@ -3722,32 +3782,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3769,32 +3829,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3816,32 +3876,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3863,32 +3923,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3910,32 +3970,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 7.0 months</t>
         </is>
@@ -3957,32 +4017,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 10.9 months</t>
         </is>
@@ -4004,17 +4064,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4029,7 +4089,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Category 1 preferred 1L mTNBC BRCA-wt/PD-L1 CPS&lt;10 — listed AHEAD of approval</t>
         </is>
@@ -4051,17 +4111,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4076,7 +4136,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -4098,32 +4158,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4145,32 +4205,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4192,32 +4252,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4239,32 +4299,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4286,32 +4346,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4333,32 +4393,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
         </is>
@@ -4380,32 +4440,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 10.4 months</t>
         </is>
@@ -4427,32 +4487,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 15.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 15.4 months</t>
         </is>
@@ -4474,32 +4534,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
         </is>
@@ -4521,32 +4581,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Nov 2028</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 23.4 months</t>
         </is>
@@ -4568,32 +4628,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 14.3 months</t>
         </is>
@@ -4615,22 +4675,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4640,7 +4700,7 @@
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Targeting rapid launch post-approval</t>
         </is>
@@ -4662,32 +4722,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-10-01)</t>
         </is>
@@ -4709,32 +4769,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
         </is>
@@ -4756,32 +4816,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2027-09-04, HTA 2027-12-13)</t>
         </is>
@@ -4803,32 +4863,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-09-04, EMA 2027-03-11). G-BA does not gate access.</t>
         </is>
@@ -4850,32 +4910,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
         </is>
@@ -4897,32 +4957,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Nov 2028</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-09-04, HTA 2028-08-13)</t>
         </is>
@@ -4944,32 +5004,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-11-10)</t>
         </is>
@@ -4979,6 +5039,13 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5033,7 +5100,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -5043,7 +5110,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -5080,22 +5147,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5105,7 +5172,7 @@
           <t>ClinicalTrials.gov NCT05382299 (estimated)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>ASCENT-04 estimated primary completion</t>
         </is>
@@ -5127,32 +5194,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Estimated; full dataset published NEJM 21 Jan 2026</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
+          <t>NEJM publication — 21 Jan 2026</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Full ASCENT-04 data published NEJM supporting Category 1 upgrade</t>
         </is>
@@ -5174,22 +5241,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5199,7 +5266,7 @@
           <t>Projected based on Gilead H2 2026 launch target</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>May come slightly after ASCENT-03 monotherapy approval</t>
         </is>
@@ -5221,32 +5288,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5268,32 +5335,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5315,32 +5382,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5362,32 +5429,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5409,32 +5476,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 7.0 months</t>
         </is>
@@ -5456,32 +5523,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 10.9 months</t>
         </is>
@@ -5503,17 +5570,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5528,7 +5595,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Initially Category 2A preferred; upgraded to Category 1 in v2.2026</t>
         </is>
@@ -5550,17 +5617,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5575,7 +5642,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5593,32 +5660,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5640,32 +5707,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5687,32 +5754,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5734,32 +5801,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5781,32 +5848,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5828,32 +5895,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
         </is>
@@ -5875,32 +5942,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 10.4 months</t>
         </is>
@@ -5922,32 +5989,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 15.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 15.4 months</t>
         </is>
@@ -5969,32 +6036,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
         </is>
@@ -6016,32 +6083,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 23.4 months</t>
         </is>
@@ -6063,32 +6130,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 14.3 months</t>
         </is>
@@ -6110,22 +6177,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6135,7 +6202,7 @@
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Combo launch may follow monotherapy by ~1 month</t>
         </is>
@@ -6157,32 +6224,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-11-01)</t>
         </is>
@@ -6204,32 +6271,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
         </is>
@@ -6251,32 +6318,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2027-10-04, HTA 2028-01-12)</t>
         </is>
@@ -6298,32 +6365,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-10-04, EMA 2027-04-10). G-BA does not gate access.</t>
         </is>
@@ -6345,32 +6412,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
         </is>
@@ -6392,32 +6459,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-10-04, HTA 2028-09-12)</t>
         </is>
@@ -6439,32 +6506,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-12-10)</t>
         </is>
@@ -6474,6 +6541,14 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6528,7 +6603,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -6538,7 +6613,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -6575,22 +6650,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6600,7 +6675,7 @@
           <t>ClinicalTrials.gov NCT05104866 (estimated)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>TROPION-Breast02 primary completion estimate</t>
         </is>
@@ -6622,32 +6697,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Data presented at major congress</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Primary data supported sBLA submission</t>
         </is>
@@ -6669,22 +6744,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -6694,7 +6769,7 @@
           <t>PDUFA Q2 2026 under Priority Review</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Priority Review granted Feb 2026; PDUFA target date Q2 2026</t>
         </is>
@@ -6716,22 +6791,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6741,7 +6816,7 @@
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6759,22 +6834,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6784,7 +6859,7 @@
           <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Based on regulatory submission accepted Dec 2025</t>
         </is>
@@ -6806,22 +6881,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6831,7 +6906,7 @@
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6849,22 +6924,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6874,7 +6949,7 @@
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6892,32 +6967,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 7.0 months</t>
         </is>
@@ -6939,32 +7014,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 10.9 months</t>
         </is>
@@ -6986,17 +7061,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7011,7 +7086,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Category 2A other recommended; upgraded to Category 2A preferred in v2.2026</t>
         </is>
@@ -7033,17 +7108,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7058,7 +7133,7 @@
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7076,32 +7151,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7123,32 +7198,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7170,32 +7245,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7217,32 +7292,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7264,32 +7339,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7311,32 +7386,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
         </is>
@@ -7358,32 +7433,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 10.4 months</t>
         </is>
@@ -7405,32 +7480,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 15.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 15.4 months</t>
         </is>
@@ -7452,32 +7527,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
         </is>
@@ -7499,32 +7574,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 23.4 months</t>
         </is>
@@ -7546,32 +7621,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 14.3 months</t>
         </is>
@@ -7593,22 +7668,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -7618,7 +7693,7 @@
           <t>Projected post-PDUFA</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Expected rapid US launch following FDA approval</t>
         </is>
@@ -7640,32 +7715,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-07-01)</t>
         </is>
@@ -7687,32 +7762,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
         </is>
@@ -7734,32 +7809,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2027-06-04, HTA 2027-09-12)</t>
         </is>
@@ -7781,32 +7856,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-06-04, EMA 2026-09-01). G-BA does not gate access.</t>
         </is>
@@ -7828,32 +7903,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
         </is>
@@ -7875,32 +7950,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-06-04, HTA 2028-05-13)</t>
         </is>
@@ -7922,32 +7997,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-08-10)</t>
         </is>
@@ -7957,6 +8032,17 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8011,7 +8097,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -8021,7 +8107,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -8058,22 +8144,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8083,7 +8169,7 @@
           <t>Estimated: '~18 months out' as of Apr 2026</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>GAP: Exact PCD depends on enrollment pace; verify ClinicalTrials.gov</t>
         </is>
@@ -8105,32 +8191,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Estimated: ~5 months post-PCD for major congress presentation</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Assumes data maturation + congress cycle</t>
         </is>
@@ -8152,32 +8238,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Projected: ~6-10 months post-submission</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Assumes standard or Priority Review</t>
         </is>
@@ -8199,32 +8285,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8246,32 +8332,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="11" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8293,32 +8379,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8340,32 +8426,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8387,32 +8473,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Sep 2029</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 7.0 months</t>
         </is>
@@ -8434,32 +8520,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Apr 2030</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 10.9 months</t>
         </is>
@@ -8481,32 +8567,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8528,32 +8614,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8575,32 +8661,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8622,32 +8708,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8669,32 +8755,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8716,32 +8802,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8763,32 +8849,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8810,32 +8896,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
         </is>
@@ -8857,32 +8943,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Sep 2029</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Dec 2029</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 10.4 months</t>
         </is>
@@ -8904,32 +8990,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Apr 2030</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>May 2030</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 15.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 15.4 months</t>
         </is>
@@ -8951,32 +9037,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Jul 2030</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>Nov 2030</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
         </is>
@@ -8998,32 +9084,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>Aug 2030</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Dec 2030</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>Mar 2031</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 23.4 months</t>
         </is>
@@ -9045,32 +9131,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 14.3 months</t>
         </is>
@@ -9092,32 +9178,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Projected post-FDA approval</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -9135,32 +9221,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2029-01-28, launch 2029-02-01)</t>
         </is>
@@ -9182,32 +9268,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
         </is>
@@ -9229,32 +9315,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
         <is>
           <t>Apr 2030</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>May 2030</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2030-01-04, HTA 2030-04-14)</t>
         </is>
@@ -9276,32 +9362,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F31" s="11" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2030-01-04, EMA 2029-07-11). G-BA does not gate access.</t>
         </is>
@@ -9323,32 +9409,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Jul 2030</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>Nov 2030</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
         </is>
@@ -9370,32 +9456,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Aug 2030</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Dec 2030</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>Mar 2031</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2030-01-04, HTA 2030-12-14)</t>
         </is>
@@ -9417,32 +9503,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="11" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2029-01-28, HTA 2030-03-12)</t>
         </is>
@@ -9452,6 +9538,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9476,7 +9565,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Assumptions &amp; Data Gaps Log</t>
         </is>
@@ -9535,7 +9624,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>FDA approval date is used as T=0 anchor for all market-relative lag projections.</t>
         </is>
@@ -9560,7 +9649,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -9573,7 +9662,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Two analogs bracket the projection range: Enhertu 2L+ HER2+ mBC (optimistic) and Trodelvy 3L+ mTNBC (conservative).</t>
         </is>
@@ -9598,7 +9687,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -9611,7 +9700,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>SoC integration is defined as the LATER of (a) guideline inclusion and (b) national reimbursement/access.</t>
         </is>
@@ -9636,7 +9725,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -9649,7 +9738,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>For Germany, SoC integration uses EMA approval date (not G-BA) as access is available during free-pricing period under AMNOG.</t>
         </is>
@@ -9674,7 +9763,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9687,7 +9776,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>For US, SoC integration = max(NCCN guideline inclusion, commercial launch date). No HTA gate.</t>
         </is>
@@ -9712,7 +9801,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9725,7 +9814,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>EMA centralized procedure assumed for all EU5 markets; no national divergence.</t>
         </is>
@@ -9750,7 +9839,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9763,7 +9852,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>MHRA assumed to follow EMA via Great Britain reliance pathway, adding 0-2 months to EMA date.</t>
         </is>
@@ -9788,7 +9877,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9801,7 +9890,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Health Canada assumed to run parallel review; typically 6-15 months post-FDA based on analogs.</t>
         </is>
@@ -9826,7 +9915,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -9839,7 +9928,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Dato-DXd (TROPION-Breast02) PDUFA target Q2 2026 based on FDA Priority Review grant Feb 2026.</t>
         </is>
@@ -9864,7 +9953,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -9877,7 +9966,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-03) FDA approval targeted H2 2026 based on Gilead Q4 2025 Earnings guidance for accelerated launch.</t>
         </is>
@@ -9902,7 +9991,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -9915,7 +10004,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-04 combo) FDA approval expected H2 2026, possibly 1-2 months after ASCENT-03 monotherapy.</t>
         </is>
@@ -9940,7 +10029,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -9953,7 +10042,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>Dato-DXd EU/China approval projected as early as Q3 2026 per Daiichi Q3 FY2025 Earnings guidance, based on regulatory submission accepted Dec 2025.</t>
         </is>
@@ -9978,7 +10067,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -9991,7 +10080,7 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>TROPION-Breast05 (Dato-DXd CPS&gt;=10) PCD estimated Oct 2027, based on '~18 months out' as of Apr 2026.</t>
         </is>
@@ -10011,12 +10100,12 @@
           <t>Dato-DXd</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10033,7 +10122,7 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>ASCENT-03 and ASCENT-04 primary completion dates estimated mid-2025; exact dates need verification on ClinicalTrials.gov.</t>
         </is>
@@ -10053,12 +10142,12 @@
           <t>Trodelvy</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10075,7 +10164,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>NCCN already lists both Trodelvy and Dato-DXd for 1L mTNBC pre-approval (v1.2026 and v2.2026). NCCN guideline milestone is therefore BEFORE FDA approval — unusual but confirmed.</t>
         </is>
@@ -10100,7 +10189,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10113,7 +10202,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>ESMO guideline inclusion for 1L TNBC ADCs assumed to follow within 6-12 months of FDA approval, based on analog precedent.</t>
         </is>
@@ -10138,7 +10227,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10151,7 +10240,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>Trodelvy Category 1 vs Dato-DXd Category 2A reflects greater evidence maturity (inc. OS data in 2L), not lack of support for Dato-DXd.</t>
         </is>
@@ -10176,7 +10265,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10189,7 +10278,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>NICE appraisal timelines assumed 12-28 months post-FDA based on analogs. CDF route possible for Dato-DXd given weaker evidence vs Trodelvy.</t>
         </is>
@@ -10214,7 +10303,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10227,7 +10316,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>G-BA AMNOG assessment assumed within 3-6 months of EMA approval; does not gate market access in Germany.</t>
         </is>
@@ -10252,7 +10341,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10265,7 +10354,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>HAS (France) transparency committee opinion assumed 8-17 months post-FDA; pricing negotiation adds further time.</t>
         </is>
@@ -10290,7 +10379,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10303,7 +10392,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>AIFA (Italy) reimbursement assumed 18-24 months post-FDA; typically slowest EU5 market.</t>
         </is>
@@ -10328,7 +10417,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10341,7 +10430,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>AEMPS/Spain reimbursement assumed 20-27 months post-FDA; national + regional pricing layers add variability.</t>
         </is>
@@ -10366,7 +10455,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10379,7 +10468,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>CADTH/pCODR (Canada) recommendation assumed 12-20 months post-FDA; provincial listing adds further time.</t>
         </is>
@@ -10404,7 +10493,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10417,7 +10506,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>HAS (France) exact decision dates for both analogs need primary research from HAS public database.</t>
         </is>
@@ -10437,12 +10526,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10459,7 +10548,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>AIFA (Italy) exact GU publication dates for both analogs need primary research.</t>
         </is>
@@ -10479,12 +10568,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10501,7 +10590,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>AEMPS (Spain) exact pricing/reimbursement dates for both analogs need primary research.</t>
         </is>
@@ -10521,12 +10610,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10543,7 +10632,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>G-BA exact AMNOG decision dates for both analogs need verification against G-BA public records.</t>
         </is>
@@ -10563,12 +10652,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10585,7 +10674,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>ESMO guideline exact update dates for both analogs are approximate; need verification against ESMO publications.</t>
         </is>
@@ -10605,12 +10694,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10627,7 +10716,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>Trodelvy's Category 1 preferred NCCN status and broader 1L population coverage (CPS&lt;10 AND CPS&gt;=10) gives it a competitive advantage over Dato-DXd at launch.</t>
         </is>
@@ -10652,7 +10741,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10665,7 +10754,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>Both ADCs have NCCN recommendations ahead of regulatory approval — unusual precedent that may accelerate SoC integration in US.</t>
         </is>
@@ -10690,7 +10779,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10735,22 +10824,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&lt;10 (ASCENT-03)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&gt;=10 (ASCENT-04)</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&lt;10 (TB02)</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&gt;=10 (TB05)</t>
         </is>
@@ -10814,7 +10903,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>N/A (Commercial)</t>
         </is>
@@ -10824,7 +10913,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Narrow (6mo) — prioritize now</t>
         </is>
@@ -10834,7 +10923,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Narrow (7mo) — prioritize now</t>
         </is>
@@ -10844,7 +10933,7 @@
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>Narrow (3mo) — prioritize now</t>
         </is>
@@ -10854,7 +10943,7 @@
           <t>Q1 2029</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Extended (34mo) — flexible timing</t>
         </is>
@@ -10866,7 +10955,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>NICE</t>
         </is>
@@ -10876,7 +10965,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -10886,7 +10975,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Extended (26mo) — flexible timing</t>
         </is>
@@ -10896,7 +10985,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>Moderate (22mo) — plan enrollment</t>
         </is>
@@ -10906,7 +10995,7 @@
           <t>Q3 2030</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Extended (53mo) — flexible timing</t>
         </is>
@@ -10918,7 +11007,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>HAS (Transparency Committee)</t>
         </is>
@@ -10928,7 +11017,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>Moderate (20mo) — plan enrollment</t>
         </is>
@@ -10938,7 +11027,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>Moderate (21mo) — plan enrollment</t>
         </is>
@@ -10948,7 +11037,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>Moderate (17mo) — plan enrollment</t>
         </is>
@@ -10958,7 +11047,7 @@
           <t>Q2 2030</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>Extended (48mo) — flexible timing</t>
         </is>
@@ -10970,7 +11059,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>G-BA (AMNOG)</t>
         </is>
@@ -10980,7 +11069,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Moderate (17mo) — plan enrollment</t>
         </is>
@@ -10990,7 +11079,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>Moderate (18mo) — plan enrollment</t>
         </is>
@@ -11000,7 +11089,7 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>Moderate (14mo) — plan enrollment</t>
         </is>
@@ -11010,7 +11099,7 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>Extended (45mo) — flexible timing</t>
         </is>
@@ -11022,7 +11111,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>AIFA</t>
         </is>
@@ -11032,7 +11121,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -11042,7 +11131,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>Extended (26mo) — flexible timing</t>
         </is>
@@ -11052,7 +11141,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Moderate (22mo) — plan enrollment</t>
         </is>
@@ -11062,7 +11151,7 @@
           <t>Q3 2030</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>Extended (53mo) — flexible timing</t>
         </is>
@@ -11074,7 +11163,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>AEMPS / IPT</t>
         </is>
@@ -11084,7 +11173,7 @@
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Extended (28mo) — flexible timing</t>
         </is>
@@ -11094,7 +11183,7 @@
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>Extended (29mo) — flexible timing</t>
         </is>
@@ -11104,7 +11193,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="H10" s="20" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -11114,7 +11203,7 @@
           <t>Q4 2030</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>Extended (56mo) — flexible timing</t>
         </is>
@@ -11126,7 +11215,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>CADTH / pCODR</t>
         </is>
@@ -11136,7 +11225,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Moderate (19mo) — plan enrollment</t>
         </is>
@@ -11146,7 +11235,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>Moderate (20mo) — plan enrollment</t>
         </is>
@@ -11156,7 +11245,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="H11" s="22" t="inlineStr">
         <is>
           <t>Moderate (16mo) — plan enrollment</t>
         </is>
@@ -11166,63 +11255,63 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J11" s="20" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>Extended (47mo) — flexible timing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Key Findings</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>US: NCCN already includes both Trodelvy and Dato-DXd pre-approval. SoC integration will occur at commercial launch (H2 2026).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>Germany: Access available at EMA approval (free pricing period). Among earliest EU5 markets for SoC shift.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>UK: NICE CDF pathway likely for newer ADCs. Full SoC integration may lag 12-28 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>France/Italy/Spain: Longest reimbursement timelines (12-27 months post-FDA). Extended enrollment windows.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Canada: Moderate timeline. CADTH recommendation typically 12-20 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>Dato-DXd CPS&gt;=10 (TROPION-Breast05): Significantly behind — PCD ~Oct 2027, FDA ~2029. Extended window in all markets.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="24" t="inlineStr">
         <is>
           <t>Implication: Geographies with longer HTA timelines (IT, ES, FR) offer wider pre-SoC enrollment windows for Corcept's Phase 3.</t>
         </is>

--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -67,7 +67,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2F3"/>
-        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -172,14 +166,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -196,29 +190,23 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -675,7 +663,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -690,12 +678,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT03529110</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>DESTINY-Breast03 primary analysis cutoff</t>
         </is>
@@ -717,7 +705,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Sep 2021</t>
         </is>
@@ -732,12 +720,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>ESMO 2021 presentation</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>First presentation at ESMO Congress 2021</t>
         </is>
@@ -759,7 +747,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Aug 2022</t>
         </is>
@@ -770,12 +758,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Full approval for 2L+ HER2+ mBC based on DESTINY-Breast03</t>
         </is>
@@ -797,7 +785,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Jan 2023</t>
         </is>
@@ -812,12 +800,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>EMA centralized procedure; EC marketing authorization</t>
         </is>
@@ -839,7 +827,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Jan 2023</t>
         </is>
@@ -854,12 +842,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Same EMA approval applies to all EU5</t>
         </is>
@@ -881,7 +869,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Jan 2023</t>
         </is>
@@ -896,12 +884,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -919,7 +907,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Jan 2023</t>
         </is>
@@ -934,12 +922,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -957,7 +945,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Jan 2023</t>
         </is>
@@ -972,12 +960,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>MHRA GBR reliance procedure</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>MHRA followed EMA timeline via reliance pathway</t>
         </is>
@@ -999,7 +987,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Feb 2023</t>
         </is>
@@ -1014,12 +1002,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1037,7 +1025,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sep 2022</t>
         </is>
@@ -1052,12 +1040,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Category 1 preferred within ~1 month of FDA approval</t>
         </is>
@@ -1079,7 +1067,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Sep 2022</t>
         </is>
@@ -1094,12 +1082,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -1121,7 +1109,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1136,12 +1124,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Updated recommendation following full publication</t>
         </is>
@@ -1163,7 +1151,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1178,12 +1166,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1201,7 +1189,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1216,12 +1204,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1239,7 +1227,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1254,12 +1242,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1277,7 +1265,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Sep 2023</t>
         </is>
@@ -1292,12 +1280,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline 2023</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1315,7 +1303,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Oct 2023</t>
         </is>
@@ -1330,12 +1318,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>NICE TA942</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Recommended for routine commissioning</t>
         </is>
@@ -1357,29 +1345,29 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>May 2023</t>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>G-BA AMNOG assessment</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>GAP: Exact G-BA decision date needs verification. Considerable additional benefit; approximate date.</t>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>G-BA Beschluss — procedure 2022-08-01-D-836</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Considerable additional benefit. Decision 9 days after EMA approval.</t>
         </is>
       </c>
     </row>
@@ -1399,29 +1387,29 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Oct 2023</t>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Feb 2023</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Estimated from typical HAS timeline</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>GAP: Exact HAS Transparency Committee opinion date needs research</t>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>HAS CT opinion — ENHERTU_22022023_AVIS_CT19944</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>SMR: Important; ASMR III (moderate improvement). Published online 30 Mar 2023.</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1429,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Mar 2024</t>
         </is>
@@ -1456,12 +1444,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Estimated from typical AIFA timeline</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>GAP: Exact AIFA Gazzetta Ufficiale publication date needs research</t>
         </is>
@@ -1483,7 +1471,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Apr 2024</t>
         </is>
@@ -1498,12 +1486,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Estimated from typical AEMPS/IPT timeline</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>GAP: Exact Spanish pricing/reimbursement date needs research</t>
         </is>
@@ -1525,7 +1513,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Jun 2023</t>
         </is>
@@ -1540,12 +1528,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Recommended for reimbursement with clinical criteria</t>
         </is>
@@ -1567,7 +1555,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Aug 2022</t>
         </is>
@@ -1582,12 +1570,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Daiichi Sankyo press release</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>US commercial launch within days of FDA approval</t>
         </is>
@@ -1609,7 +1597,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -1739,7 +1727,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Nov 2020</t>
         </is>
@@ -1754,12 +1742,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT02574455</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ASCENT trial primary completion</t>
         </is>
@@ -1781,7 +1769,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Sep 2020</t>
         </is>
@@ -1796,12 +1784,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>ESMO 2020 — NEJM publication</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Primary results presented at ESMO Virtual 2020</t>
         </is>
@@ -1823,7 +1811,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Apr 2021</t>
         </is>
@@ -1834,12 +1822,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Regular approval for 3L+ mTNBC (accelerated approval Apr 2020 converted)</t>
         </is>
@@ -1861,7 +1849,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Nov 2021</t>
         </is>
@@ -1876,12 +1864,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>EMA centralized procedure; ~7 months post-FDA</t>
         </is>
@@ -1903,7 +1891,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Nov 2021</t>
         </is>
@@ -1918,12 +1906,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1941,7 +1929,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Nov 2021</t>
         </is>
@@ -1956,12 +1944,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1979,7 +1967,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Nov 2021</t>
         </is>
@@ -1994,12 +1982,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2017,7 +2005,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Dec 2021</t>
         </is>
@@ -2032,12 +2020,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>MHRA approval</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>MHRA followed shortly after EMA; approximate date</t>
         </is>
@@ -2059,7 +2047,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Jul 2022</t>
         </is>
@@ -2074,12 +2062,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>~15 months post-FDA</t>
         </is>
@@ -2101,7 +2089,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>May 2021</t>
         </is>
@@ -2116,12 +2104,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Added within one update cycle of full approval</t>
         </is>
@@ -2143,7 +2131,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>May 2021</t>
         </is>
@@ -2158,12 +2146,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2181,7 +2169,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2196,12 +2184,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Approximate timing of ESMO guideline inclusion</t>
         </is>
@@ -2223,7 +2211,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2238,12 +2226,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2261,7 +2249,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2276,12 +2264,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2299,7 +2287,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2314,12 +2302,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2337,7 +2325,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Mar 2022</t>
         </is>
@@ -2352,12 +2340,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>ESMO mBC Living Guideline update</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2375,7 +2363,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Jul 2023</t>
         </is>
@@ -2390,12 +2378,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>NICE TA900</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Recommended via Cancer Drugs Fund; ~27 months post-FDA</t>
         </is>
@@ -2417,29 +2405,29 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Apr 2022</t>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>May 2022</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>G-BA AMNOG assessment</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>GAP: Exact date approximate — verify against G-BA records</t>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>G-BA Beschluss — procedure 2021-12-01-D-750</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>~6 months post-EMA approval.</t>
         </is>
       </c>
     </row>
@@ -2459,29 +2447,29 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Sep 2022</t>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Apr 2022</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Estimated from typical HAS timeline</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>GAP: Exact HAS TC opinion date for Trodelvy 3L+ needs research</t>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>HAS CT opinion — TRODELVY_06042022_AVIS_CT19684</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>SMR: Important; ASMR III (moderate improvement). Published online 2 Jun 2022.</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2489,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Mar 2023</t>
         </is>
@@ -2516,12 +2504,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Estimated from typical AIFA timeline</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>GAP: Exact AIFA GU publication date needs research</t>
         </is>
@@ -2543,7 +2531,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Jul 2023</t>
         </is>
@@ -2558,12 +2546,12 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Estimated from typical AEMPS timeline</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>GAP: Exact Spanish pricing decision date needs research</t>
         </is>
@@ -2585,7 +2573,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Oct 2022</t>
         </is>
@@ -2600,12 +2588,12 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Approximate date; ~18 months post-FDA</t>
         </is>
@@ -2627,7 +2615,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Apr 2021</t>
         </is>
@@ -2642,12 +2630,12 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Gilead press release</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>US launch shortly after FDA approval</t>
         </is>
@@ -2669,7 +2657,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2787,32 +2775,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2825,32 +2813,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2863,32 +2851,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2901,32 +2889,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2939,32 +2927,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2977,32 +2965,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>10.9</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -3015,32 +3003,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3053,32 +3041,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3091,32 +3079,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3129,32 +3117,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3167,32 +3155,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3205,32 +3193,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3243,32 +3231,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>13.3</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3281,32 +3269,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3319,32 +3307,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3357,32 +3345,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>13.9</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>16.8</t>
-        </is>
-      </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3395,32 +3383,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>18.9</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>20.9</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>22.8</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3433,32 +3421,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>19.9</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>23.4</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>26.8</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3471,32 +3459,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>14.3</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3509,32 +3497,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3594,7 +3582,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -3604,7 +3592,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -3641,34 +3629,34 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>ClinicalTrials.gov NCT05382286 (estimated)</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>ASCENT-03 estimated primary completion; verify on ClinicalTrials.gov</t>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2028</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2028</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Jul 2028</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov NCT05382299 — registered PCD</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Registered PCD Jul 2028 is for final OS analysis. PFS interim already read out.</t>
         </is>
       </c>
     </row>
@@ -3688,34 +3676,34 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Estimated based on typical PCD-to-readout lag</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Gilead targeting data for H2 2025 / H1 2026</t>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Gilead presentations / regulatory submission</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>PFS data already presented; supports sBLA filing. Trial status: Active, Not Recruiting (623 enrolled).</t>
         </is>
       </c>
     </row>
@@ -3735,32 +3723,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated 1L launch H2 2026</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Assumes standard sBLA review (~6-8 months) or Priority Review (~6 months)</t>
         </is>
@@ -3782,32 +3770,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3829,32 +3817,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3876,32 +3864,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3923,32 +3911,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3970,32 +3958,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 7.0 months</t>
         </is>
@@ -4017,32 +4005,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 10.9 months</t>
         </is>
@@ -4064,32 +4052,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Category 1 preferred 1L mTNBC BRCA-wt/PD-L1 CPS&lt;10 — listed AHEAD of approval</t>
         </is>
@@ -4111,32 +4099,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -4158,32 +4146,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4205,32 +4193,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4252,32 +4240,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4299,32 +4287,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4346,32 +4334,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
         </is>
@@ -4393,32 +4381,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
         </is>
@@ -4440,34 +4428,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>May 2027</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 10.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-09-01 + 10.4 months</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-09-01 + 9.7 months</t>
         </is>
       </c>
     </row>
@@ -4487,34 +4475,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Sep 2027</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 15.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-09-01 + 15.4 months</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-09-01 + 9.3 months</t>
         </is>
       </c>
     </row>
@@ -4534,32 +4522,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
         </is>
@@ -4581,32 +4569,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Nov 2028</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 23.4 months</t>
         </is>
@@ -4628,32 +4616,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 14.3 months</t>
         </is>
@@ -4675,32 +4663,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Targeting rapid launch post-approval</t>
         </is>
@@ -4722,32 +4710,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-10-01)</t>
         </is>
@@ -4769,32 +4757,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
         </is>
@@ -4816,34 +4804,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>France SoC = max(guideline 2027-09-04, HTA 2027-12-13)</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>France SoC = max(guideline 2027-09-04, HTA 2027-06-11)</t>
         </is>
       </c>
     </row>
@@ -4863,32 +4851,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-09-04, EMA 2027-03-11). G-BA does not gate access.</t>
         </is>
@@ -4910,32 +4898,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
         </is>
@@ -4957,32 +4945,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Nov 2028</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-09-04, HTA 2028-08-13)</t>
         </is>
@@ -5004,32 +4992,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-11-10)</t>
         </is>
@@ -5100,7 +5088,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -5110,7 +5098,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -5147,34 +5135,34 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Jun 2025</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>ClinicalTrials.gov NCT05382299 (estimated)</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>ASCENT-04 estimated primary completion</t>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov NCT05382286 — registered PCD</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Registered PCD Feb 2027 is for final OS analysis. PFS data published NEJM 21 Jan 2026.</t>
         </is>
       </c>
     </row>
@@ -5194,34 +5182,34 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Dec 2025</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>NEJM publication — 21 Jan 2026</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Full ASCENT-04 data published NEJM supporting Category 1 upgrade</t>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Full ASCENT-04 PFS dataset published; supported NCCN Category 1 upgrade. Trial: Active, Not Recruiting (443 enrolled).</t>
         </is>
       </c>
     </row>
@@ -5241,32 +5229,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Projected based on Gilead H2 2026 launch target</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>May come slightly after ASCENT-03 monotherapy approval</t>
         </is>
@@ -5288,32 +5276,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5335,32 +5323,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5382,32 +5370,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5429,32 +5417,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5476,32 +5464,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 7.0 months</t>
         </is>
@@ -5523,32 +5511,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 10.9 months</t>
         </is>
@@ -5570,32 +5558,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Initially Category 2A preferred; upgraded to Category 1 in v2.2026</t>
         </is>
@@ -5617,32 +5605,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5660,32 +5648,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5707,32 +5695,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5754,32 +5742,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5801,32 +5789,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5848,32 +5836,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
         </is>
@@ -5895,32 +5883,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
         </is>
@@ -5942,34 +5930,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Nov 2027</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 10.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-10-01 + 10.4 months</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-10-01 + 9.7 months</t>
         </is>
       </c>
     </row>
@@ -5989,34 +5977,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Feb 2028</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 15.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-10-01 + 15.4 months</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-10-01 + 9.3 months</t>
         </is>
       </c>
     </row>
@@ -6036,32 +6024,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
         </is>
@@ -6083,32 +6071,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 23.4 months</t>
         </is>
@@ -6130,32 +6118,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 14.3 months</t>
         </is>
@@ -6177,32 +6165,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Combo launch may follow monotherapy by ~1 month</t>
         </is>
@@ -6224,32 +6212,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-11-01)</t>
         </is>
@@ -6271,32 +6259,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
         </is>
@@ -6318,34 +6306,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Aug 2027</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Feb 2028</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>France SoC = max(guideline 2027-10-04, HTA 2028-01-12)</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>France SoC = max(guideline 2027-10-04, HTA 2027-07-11)</t>
         </is>
       </c>
     </row>
@@ -6365,32 +6353,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-10-04, EMA 2027-04-10). G-BA does not gate access.</t>
         </is>
@@ -6412,32 +6400,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
         </is>
@@ -6459,32 +6447,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-10-04, HTA 2028-09-12)</t>
         </is>
@@ -6506,32 +6494,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-12-10)</t>
         </is>
@@ -6603,7 +6591,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -6613,7 +6601,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -6650,32 +6638,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT05104866 (estimated)</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>TROPION-Breast02 primary completion estimate</t>
         </is>
@@ -6697,32 +6685,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Data presented at major congress</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Primary data supported sBLA submission</t>
         </is>
@@ -6744,32 +6732,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>PDUFA Q2 2026 under Priority Review</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Priority Review granted Feb 2026; PDUFA target date Q2 2026</t>
         </is>
@@ -6791,32 +6779,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6834,32 +6822,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Based on regulatory submission accepted Dec 2025</t>
         </is>
@@ -6881,32 +6869,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6924,32 +6912,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6967,32 +6955,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 7.0 months</t>
         </is>
@@ -7014,32 +7002,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 10.9 months</t>
         </is>
@@ -7061,32 +7049,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Category 2A other recommended; upgraded to Category 2A preferred in v2.2026</t>
         </is>
@@ -7108,32 +7096,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7151,32 +7139,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7198,32 +7186,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7245,32 +7233,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7292,32 +7280,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7339,32 +7327,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
         </is>
@@ -7386,32 +7374,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
         </is>
@@ -7433,34 +7421,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Feb 2027</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>May 2027</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 10.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-06-01 + 10.4 months</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-06-01 + 9.7 months</t>
         </is>
       </c>
     </row>
@@ -7480,34 +7468,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 15.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2026-06-01 + 15.4 months</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2026-06-01 + 9.3 months</t>
         </is>
       </c>
     </row>
@@ -7527,32 +7515,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
         </is>
@@ -7574,32 +7562,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 23.4 months</t>
         </is>
@@ -7621,32 +7609,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 14.3 months</t>
         </is>
@@ -7668,32 +7656,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Projected post-PDUFA</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Expected rapid US launch following FDA approval</t>
         </is>
@@ -7715,32 +7703,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-07-01)</t>
         </is>
@@ -7762,32 +7750,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
         </is>
@@ -7809,34 +7797,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>France SoC = max(guideline 2027-06-04, HTA 2027-09-12)</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>France SoC = max(guideline 2027-06-04, HTA 2027-03-11)</t>
         </is>
       </c>
     </row>
@@ -7856,32 +7844,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2027-06-04, EMA 2026-09-01). G-BA does not gate access.</t>
         </is>
@@ -7903,32 +7891,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Apr 2028</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
         </is>
@@ -7950,32 +7938,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Aug 2028</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2027-06-04, HTA 2028-05-13)</t>
         </is>
@@ -7997,32 +7985,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-08-10)</t>
         </is>
@@ -8097,7 +8085,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -8107,7 +8095,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -8144,34 +8132,34 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Estimated: '~18 months out' as of Apr 2026</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>GAP: Exact PCD depends on enrollment pace; verify ClinicalTrials.gov</t>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>ClinicalTrials.gov NCT06103864 — registered PCD</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>TROPION-Breast05. Status: Recruiting. Study completion: Sep 2030.</t>
         </is>
       </c>
     </row>
@@ -8191,32 +8179,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Estimated: ~5 months post-PCD for major congress presentation</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Assumes data maturation + congress cycle</t>
         </is>
@@ -8238,32 +8226,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Projected: ~6-10 months post-submission</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Assumes standard or Priority Review</t>
         </is>
@@ -8285,32 +8273,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8332,32 +8320,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8379,32 +8367,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8426,32 +8414,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8473,32 +8461,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Sep 2029</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 7.0 months</t>
         </is>
@@ -8520,32 +8508,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Apr 2030</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 10.9 months</t>
         </is>
@@ -8567,32 +8555,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8614,32 +8602,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8661,32 +8649,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8708,32 +8696,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8755,32 +8743,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8802,32 +8790,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8849,32 +8837,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 12.1 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
         </is>
@@ -8896,32 +8884,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
         </is>
@@ -8943,34 +8931,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Sep 2029</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>Dec 2029</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Jun 2029</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Oct 2029</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Feb 2030</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 10.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2029-01-01 + 10.4 months</t>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2029-01-01 + 9.7 months</t>
         </is>
       </c>
     </row>
@@ -8990,34 +8978,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>Apr 2030</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>May 2030</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>Oct 2029</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Jan 2030</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>Analog-based projection (base): 15.4 months post-FDA</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Projected from FDA approval 2029-01-01 + 15.4 months</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Projected from FDA approval 2029-01-01 + 9.3 months</t>
         </is>
       </c>
     </row>
@@ -9037,32 +9025,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Jul 2030</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>Nov 2030</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
         </is>
@@ -9084,32 +9072,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Aug 2030</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Dec 2030</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>Mar 2031</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 23.4 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 23.4 months</t>
         </is>
@@ -9131,32 +9119,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 14.3 months</t>
         </is>
@@ -9178,32 +9166,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="E27" s="14" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Projected post-FDA approval</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -9221,32 +9209,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="E28" s="14" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2029-01-28, launch 2029-02-01)</t>
         </is>
@@ -9268,32 +9256,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="E29" s="14" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
         </is>
@@ -9315,34 +9303,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Nov 2029</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Jan 2030</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>Apr 2030</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>May 2030</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>France SoC = max(guideline 2030-01-04, HTA 2030-04-14)</t>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>France SoC = max(guideline 2030-01-04, HTA 2029-10-11)</t>
         </is>
       </c>
     </row>
@@ -9362,32 +9350,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2030-01-04, EMA 2029-07-11). G-BA does not gate access.</t>
         </is>
@@ -9409,32 +9397,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Jul 2030</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Nov 2030</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
         </is>
@@ -9456,32 +9444,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Aug 2030</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Dec 2030</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Mar 2031</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2030-01-04, HTA 2030-12-14)</t>
         </is>
@@ -9503,32 +9491,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2029-01-28, HTA 2030-03-12)</t>
         </is>
@@ -9565,7 +9553,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Assumptions &amp; Data Gaps Log</t>
         </is>
@@ -9624,7 +9612,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>FDA approval date is used as T=0 anchor for all market-relative lag projections.</t>
         </is>
@@ -9649,7 +9637,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr"/>
+      <c r="H4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -9662,7 +9650,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Two analogs bracket the projection range: Enhertu 2L+ HER2+ mBC (optimistic) and Trodelvy 3L+ mTNBC (conservative).</t>
         </is>
@@ -9687,7 +9675,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -9700,7 +9688,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>SoC integration is defined as the LATER of (a) guideline inclusion and (b) national reimbursement/access.</t>
         </is>
@@ -9725,7 +9713,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -9738,7 +9726,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>For Germany, SoC integration uses EMA approval date (not G-BA) as access is available during free-pricing period under AMNOG.</t>
         </is>
@@ -9763,7 +9751,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9776,7 +9764,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>For US, SoC integration = max(NCCN guideline inclusion, commercial launch date). No HTA gate.</t>
         </is>
@@ -9801,7 +9789,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9814,7 +9802,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>EMA centralized procedure assumed for all EU5 markets; no national divergence.</t>
         </is>
@@ -9839,7 +9827,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9852,7 +9840,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>MHRA assumed to follow EMA via Great Britain reliance pathway, adding 0-2 months to EMA date.</t>
         </is>
@@ -9877,7 +9865,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9890,7 +9878,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Health Canada assumed to run parallel review; typically 6-15 months post-FDA based on analogs.</t>
         </is>
@@ -9915,7 +9903,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -9928,7 +9916,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Dato-DXd (TROPION-Breast02) PDUFA target Q2 2026 based on FDA Priority Review grant Feb 2026.</t>
         </is>
@@ -9953,7 +9941,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -9966,7 +9954,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-03) FDA approval targeted H2 2026 based on Gilead Q4 2025 Earnings guidance for accelerated launch.</t>
         </is>
@@ -9991,7 +9979,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10004,7 +9992,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-04 combo) FDA approval expected H2 2026, possibly 1-2 months after ASCENT-03 monotherapy.</t>
         </is>
@@ -10029,7 +10017,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10042,7 +10030,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>Dato-DXd EU/China approval projected as early as Q3 2026 per Daiichi Q3 FY2025 Earnings guidance, based on regulatory submission accepted Dec 2025.</t>
         </is>
@@ -10067,7 +10055,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10080,9 +10068,9 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>TROPION-Breast05 (Dato-DXd CPS&gt;=10) PCD estimated Oct 2027, based on '~18 months out' as of Apr 2026.</t>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>TROPION-Breast05 (NCT06103864) registered PCD is Jul 28, 2027. Status: Recruiting. Study completion Sep 2030. Confirmed via ClinicalTrials.gov API.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -10092,7 +10080,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -10100,16 +10088,12 @@
           <t>Dato-DXd</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10122,9 +10106,9 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>ASCENT-03 and ASCENT-04 primary completion dates estimated mid-2025; exact dates need verification on ClinicalTrials.gov.</t>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>ASCENT-03 (NCT05382299) registered PCD Jul 2028; ASCENT-04 (NCT05382286) registered PCD Feb 2027. Both are final OS analysis dates — PFS data already presented. Note: original NCT numbers in data were swapped, now corrected. Confirmed via ClinicalTrials.gov API.</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -10134,7 +10118,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -10142,16 +10126,12 @@
           <t>Trodelvy</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10164,7 +10144,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>NCCN already lists both Trodelvy and Dato-DXd for 1L mTNBC pre-approval (v1.2026 and v2.2026). NCCN guideline milestone is therefore BEFORE FDA approval — unusual but confirmed.</t>
         </is>
@@ -10189,7 +10169,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10202,7 +10182,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>ESMO guideline inclusion for 1L TNBC ADCs assumed to follow within 6-12 months of FDA approval, based on analog precedent.</t>
         </is>
@@ -10227,7 +10207,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10240,7 +10220,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Trodelvy Category 1 vs Dato-DXd Category 2A reflects greater evidence maturity (inc. OS data in 2L), not lack of support for Dato-DXd.</t>
         </is>
@@ -10265,7 +10245,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10278,7 +10258,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>NICE appraisal timelines assumed 12-28 months post-FDA based on analogs. CDF route possible for Dato-DXd given weaker evidence vs Trodelvy.</t>
         </is>
@@ -10303,7 +10283,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10316,7 +10296,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>G-BA AMNOG assessment assumed within 3-6 months of EMA approval; does not gate market access in Germany.</t>
         </is>
@@ -10341,7 +10321,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10354,7 +10334,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>HAS (France) transparency committee opinion assumed 8-17 months post-FDA; pricing negotiation adds further time.</t>
         </is>
@@ -10379,7 +10359,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10392,7 +10372,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>AIFA (Italy) reimbursement assumed 18-24 months post-FDA; typically slowest EU5 market.</t>
         </is>
@@ -10417,7 +10397,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10430,7 +10410,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>AEMPS/Spain reimbursement assumed 20-27 months post-FDA; national + regional pricing layers add variability.</t>
         </is>
@@ -10455,7 +10435,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10468,7 +10448,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>CADTH/pCODR (Canada) recommendation assumed 12-20 months post-FDA; provincial listing adds further time.</t>
         </is>
@@ -10493,7 +10473,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10506,9 +10486,9 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>HAS (France) exact decision dates for both analogs need primary research from HAS public database.</t>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>HAS (France) decision dates confirmed: Enhertu CT opinion 22 Feb 2023, Trodelvy CT opinion 6 Apr 2022. Sourced from has-sante.fr.</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -10518,7 +10498,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -10526,16 +10506,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10548,7 +10524,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>AIFA (Italy) exact GU publication dates for both analogs need primary research.</t>
         </is>
@@ -10568,12 +10544,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10590,7 +10566,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>AEMPS (Spain) exact pricing/reimbursement dates for both analogs need primary research.</t>
         </is>
@@ -10610,12 +10586,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10632,9 +10608,9 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>G-BA exact AMNOG decision dates for both analogs need verification against G-BA public records.</t>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>G-BA AMNOG dates confirmed: Enhertu Beschluss 2 Feb 2023 (procedure D-836), Trodelvy Beschluss 19 May 2022 (procedure D-750). Sourced from g-ba.de.</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -10644,7 +10620,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -10652,16 +10628,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -10674,7 +10646,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>ESMO guideline exact update dates for both analogs are approximate; need verification against ESMO publications.</t>
         </is>
@@ -10694,12 +10666,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Requires primary research</t>
         </is>
@@ -10716,7 +10688,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Trodelvy's Category 1 preferred NCCN status and broader 1L population coverage (CPS&lt;10 AND CPS&gt;=10) gives it a competitive advantage over Dato-DXd at launch.</t>
         </is>
@@ -10741,7 +10713,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10754,7 +10726,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Both ADCs have NCCN recommendations ahead of regulatory approval — unusual precedent that may accelerate SoC integration in US.</t>
         </is>
@@ -10779,7 +10751,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10824,22 +10796,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&lt;10 (ASCENT-03)</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&gt;=10 (ASCENT-04)</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&lt;10 (TB02)</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&gt;=10 (TB05)</t>
         </is>
@@ -10903,7 +10875,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>N/A (Commercial)</t>
         </is>
@@ -10913,7 +10885,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Narrow (6mo) — prioritize now</t>
         </is>
@@ -10923,7 +10895,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Narrow (7mo) — prioritize now</t>
         </is>
@@ -10933,7 +10905,7 @@
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>Narrow (3mo) — prioritize now</t>
         </is>
@@ -10943,7 +10915,7 @@
           <t>Q1 2029</t>
         </is>
       </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="17" t="inlineStr">
         <is>
           <t>Extended (34mo) — flexible timing</t>
         </is>
@@ -10955,7 +10927,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>NICE</t>
         </is>
@@ -10965,7 +10937,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -10975,7 +10947,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>Extended (26mo) — flexible timing</t>
         </is>
@@ -10985,7 +10957,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>Moderate (22mo) — plan enrollment</t>
         </is>
@@ -10995,7 +10967,7 @@
           <t>Q3 2030</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>Extended (53mo) — flexible timing</t>
         </is>
@@ -11007,49 +10979,49 @@
           <t>France</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>HAS (Transparency Committee)</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (17mo) — plan enrollment</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (20mo) — plan enrollment</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Q1 2028</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (21mo) — plan enrollment</t>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (18mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>Moderate (17mo) — plan enrollment</t>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (14mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Q2 2030</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t>Extended (48mo) — flexible timing</t>
+          <t>Q1 2030</t>
+        </is>
+      </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>Extended (45mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11031,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>G-BA (AMNOG)</t>
         </is>
@@ -11069,7 +11041,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Moderate (17mo) — plan enrollment</t>
         </is>
@@ -11079,7 +11051,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>Moderate (18mo) — plan enrollment</t>
         </is>
@@ -11089,7 +11061,7 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>Moderate (14mo) — plan enrollment</t>
         </is>
@@ -11099,7 +11071,7 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>Extended (45mo) — flexible timing</t>
         </is>
@@ -11111,7 +11083,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>AIFA</t>
         </is>
@@ -11121,7 +11093,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -11131,7 +11103,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Extended (26mo) — flexible timing</t>
         </is>
@@ -11141,7 +11113,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>Moderate (22mo) — plan enrollment</t>
         </is>
@@ -11151,7 +11123,7 @@
           <t>Q3 2030</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>Extended (53mo) — flexible timing</t>
         </is>
@@ -11163,7 +11135,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>AEMPS / IPT</t>
         </is>
@@ -11173,7 +11145,7 @@
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Extended (28mo) — flexible timing</t>
         </is>
@@ -11183,7 +11155,7 @@
           <t>Q3 2028</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Extended (29mo) — flexible timing</t>
         </is>
@@ -11193,7 +11165,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -11203,7 +11175,7 @@
           <t>Q4 2030</t>
         </is>
       </c>
-      <c r="J10" s="21" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>Extended (56mo) — flexible timing</t>
         </is>
@@ -11215,7 +11187,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>CADTH / pCODR</t>
         </is>
@@ -11225,7 +11197,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>Moderate (19mo) — plan enrollment</t>
         </is>
@@ -11235,7 +11207,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>Moderate (20mo) — plan enrollment</t>
         </is>
@@ -11245,7 +11217,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>Moderate (16mo) — plan enrollment</t>
         </is>
@@ -11255,63 +11227,63 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Extended (47mo) — flexible timing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Key Findings</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>US: NCCN already includes both Trodelvy and Dato-DXd pre-approval. SoC integration will occur at commercial launch (H2 2026).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Germany: Access available at EMA approval (free pricing period). Among earliest EU5 markets for SoC shift.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>UK: NICE CDF pathway likely for newer ADCs. Full SoC integration may lag 12-28 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>France/Italy/Spain: Longest reimbursement timelines (12-27 months post-FDA). Extended enrollment windows.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Canada: Moderate timeline. CADTH recommendation typically 12-20 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Dato-DXd CPS&gt;=10 (TROPION-Breast05): Significantly behind — PCD ~Oct 2027, FDA ~2029. Extended window in all markets.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Implication: Geographies with longer HTA timelines (IT, ES, FR) offer wider pre-SoC enrollment windows for Corcept's Phase 3.</t>
         </is>

--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -88,26 +88,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,10 +203,10 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1109,29 +1109,29 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2023</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline 2023</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Updated recommendation following full publication</t>
+          <t>T-DXd recommended as new standard 2L therapy for HER2+ mBC. Living Guideline format launched 11 May 2023.</t>
         </is>
       </c>
     </row>
@@ -1151,24 +1151,24 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2023</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline 2023</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -1189,24 +1189,24 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2023</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline 2023</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -1227,24 +1227,24 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2023</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline 2023</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -1265,24 +1265,24 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2023</t>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline 2023</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -1429,29 +1429,29 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Mar 2024</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Jul 2023</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Estimated from typical AIFA timeline</t>
+          <t>AIFA — GU Serie Generale n.153, 3 Jul 2023</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>GAP: Exact AIFA Gazzetta Ufficiale publication date needs research</t>
+          <t>SSN reimbursement effective 4 Jul 2023. ~5 months post-EMA — faster than typical due to innovative drug status.</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Apr 2024</t>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Estimated from typical AEMPS/IPT timeline</t>
+          <t>CIPM financing decision — 28 Oct 2022</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>GAP: Exact Spanish pricing/reimbursement date needs research</t>
+          <t>SNS prescription available ~Dec 2022. Based on earlier EMA type II variation (Mar 2022), not Jan 2023 broadened indication.</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2169,29 +2169,29 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2022</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline update</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Approximate timing of ESMO guideline inclusion</t>
+          <t>SG recommended as preferred treatment after anthracyclines and taxanes for mTNBC.</t>
         </is>
       </c>
     </row>
@@ -2211,24 +2211,24 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2022</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline update</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr"/>
@@ -2249,24 +2249,24 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2022</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline update</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
@@ -2287,24 +2287,24 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2022</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline update</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr"/>
@@ -2325,24 +2325,24 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Mar 2022</t>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2021</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ESMO mBC Living Guideline update</t>
+          <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -2489,29 +2489,29 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Mar 2023</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Aug 2022</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Estimated from typical AIFA timeline</t>
+          <t>AIFA — GU Serie Generale n.185, 9 Aug 2022</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>GAP: Exact AIFA GU publication date needs research</t>
+          <t>SSN reimbursement effective 10 Aug 2022. Access via Fund for Innovative Drugs. ~9 months post-EMA.</t>
         </is>
       </c>
     </row>
@@ -2531,29 +2531,29 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2023</t>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2022</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Known</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Estimated from typical AEMPS timeline</t>
+          <t>CIPM financing decision — 28 Oct 2022</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>GAP: Exact Spanish pricing decision date needs research</t>
+          <t>Same CIPM session approved both Trodelvy and Enhertu. SNS prescription available ~Dec 2022. ~12 months post-EMA.</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Oct 2022</t>
         </is>
@@ -2657,7 +2657,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2775,17 +2775,17 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2795,7 +2795,7 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -2813,17 +2813,17 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2833,7 +2833,7 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -2851,17 +2851,17 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2871,7 +2871,7 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -2889,17 +2889,17 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2909,7 +2909,7 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>7.1</t>
         </is>
@@ -2927,17 +2927,17 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -2947,7 +2947,7 @@
           <t>7.0</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>8.3</t>
         </is>
@@ -2965,17 +2965,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -2985,7 +2985,7 @@
           <t>10.9</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>15.4</t>
         </is>
@@ -3003,17 +3003,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
@@ -3023,7 +3023,7 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
@@ -3041,17 +3041,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
@@ -3061,7 +3061,7 @@
           <t>0.9</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
@@ -3079,29 +3079,29 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>10.8</t>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>13.3</t>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
@@ -3117,29 +3117,29 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>10.8</t>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>13.3</t>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr"/>
@@ -3155,29 +3155,29 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>10.8</t>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>13.3</t>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
@@ -3193,29 +3193,29 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>10.8</t>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>13.3</t>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
@@ -3231,29 +3231,29 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>10.8</t>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>13.3</t>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>6.4</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
@@ -3269,17 +3269,17 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>14.7</t>
         </is>
@@ -3289,7 +3289,7 @@
           <t>20.9</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>27.2</t>
         </is>
@@ -3307,17 +3307,17 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -3327,7 +3327,7 @@
           <t>9.7</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
@@ -3345,17 +3345,17 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>6.6</t>
         </is>
@@ -3365,7 +3365,7 @@
           <t>9.3</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>12.0</t>
         </is>
@@ -3383,29 +3383,29 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>22.8</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>18.9</t>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>10.9</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>22.8</t>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>16.1</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
@@ -3421,29 +3421,29 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>19.9</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>26.8</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>19.9</t>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>2.8</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>23.4</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>26.8</t>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>18.7</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
@@ -3459,17 +3459,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -3479,7 +3479,7 @@
           <t>14.3</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>17.8</t>
         </is>
@@ -3497,17 +3497,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
@@ -3517,7 +3517,7 @@
           <t>0.3</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
@@ -3629,7 +3629,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
@@ -3639,7 +3639,7 @@
           <t>Jul 2028</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Jul 2028</t>
         </is>
@@ -3676,7 +3676,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -3686,7 +3686,7 @@
           <t>Dec 2025</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -3723,7 +3723,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -3733,7 +3733,7 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -3770,7 +3770,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -3780,12 +3780,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3817,7 +3817,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -3827,12 +3827,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3864,7 +3864,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -3874,12 +3874,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3911,7 +3911,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -3921,12 +3921,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3958,7 +3958,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -3968,12 +3968,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4005,7 +4005,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -4015,12 +4015,12 @@
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4052,7 +4052,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4062,7 +4062,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4099,7 +4099,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4109,7 +4109,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -4146,34 +4146,34 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -4193,34 +4193,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -4240,34 +4240,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -4287,34 +4287,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -4334,34 +4334,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
@@ -4391,12 +4391,12 @@
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4428,7 +4428,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -4438,12 +4438,12 @@
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4475,7 +4475,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -4485,12 +4485,12 @@
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4522,34 +4522,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Mar 2028</t>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2028</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Jan 2028</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 13.5 months</t>
         </is>
       </c>
     </row>
@@ -4569,34 +4569,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2028</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 23.4 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 23.4 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
@@ -4626,12 +4626,12 @@
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4663,7 +4663,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -4673,7 +4673,7 @@
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -4710,7 +4710,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -4720,12 +4720,12 @@
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4757,7 +4757,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
@@ -4767,12 +4767,12 @@
           <t>May 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Dec 2028</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
+          <t>UK SoC = max(guideline 2026-07-18, HTA 2028-05-29)</t>
         </is>
       </c>
     </row>
@@ -4804,22 +4804,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
+          <t>Jun 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2027-09-04, HTA 2027-06-11)</t>
+          <t>France SoC = max(guideline 2026-07-18, HTA 2027-06-11)</t>
         </is>
       </c>
     </row>
@@ -4851,22 +4851,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Feb 2027</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2027-09-04, EMA 2027-03-11). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-07-18, EMA 2027-03-11). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -4898,22 +4898,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Mar 2028</t>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Jul 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2028</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Jan 2028</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2027-09-04, HTA 2028-05-29)</t>
+          <t>Italy SoC = max(guideline 2026-07-18, HTA 2027-10-16)</t>
         </is>
       </c>
     </row>
@@ -4945,22 +4945,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2028</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2027-09-04, HTA 2028-08-13)</t>
+          <t>Spain SoC = max(guideline 2026-07-18, HTA 2027-07-26)</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
@@ -5002,12 +5002,12 @@
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5135,7 +5135,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -5145,7 +5145,7 @@
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
@@ -5182,7 +5182,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5192,7 +5192,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5229,7 +5229,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -5239,7 +5239,7 @@
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
@@ -5276,7 +5276,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5286,12 +5286,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5323,7 +5323,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5333,12 +5333,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5370,7 +5370,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5380,12 +5380,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5417,7 +5417,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5427,12 +5427,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>May 2027</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5464,7 +5464,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5474,12 +5474,12 @@
           <t>May 2027</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5511,7 +5511,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
@@ -5521,12 +5521,12 @@
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Jan 2028</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5558,7 +5558,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5568,7 +5568,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5605,7 +5605,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5615,7 +5615,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -5648,34 +5648,34 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -5695,34 +5695,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -5742,34 +5742,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -5789,34 +5789,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -5836,34 +5836,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
@@ -5893,12 +5893,12 @@
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5930,7 +5930,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Mar 2027</t>
         </is>
@@ -5940,12 +5940,12 @@
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5977,7 +5977,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
@@ -5987,12 +5987,12 @@
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6024,34 +6024,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+          <t>Nov 2027</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Feb 2028</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 13.5 months</t>
         </is>
       </c>
     </row>
@@ -6071,34 +6071,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>May 2028</t>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Dec 2028</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+          <t>Aug 2027</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2028</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 23.4 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 23.4 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
@@ -6128,12 +6128,12 @@
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6165,7 +6165,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
@@ -6175,7 +6175,7 @@
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
@@ -6212,7 +6212,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
@@ -6222,12 +6222,12 @@
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6259,7 +6259,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Dec 2027</t>
         </is>
@@ -6269,12 +6269,12 @@
           <t>Jun 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
+          <t>UK SoC = max(guideline 2026-08-17, HTA 2028-06-28)</t>
         </is>
       </c>
     </row>
@@ -6306,22 +6306,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
           <t>Oct 2027</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2027-10-04, HTA 2027-07-11)</t>
+          <t>France SoC = max(guideline 2026-08-17, HTA 2027-07-11)</t>
         </is>
       </c>
     </row>
@@ -6353,22 +6353,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2027</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2027</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2027</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>May 2027</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2027-10-04, EMA 2027-04-10). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-08-17, EMA 2027-04-10). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -6400,22 +6400,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+          <t>Nov 2027</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Feb 2028</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2027-10-04, HTA 2028-06-28)</t>
+          <t>Italy SoC = max(guideline 2026-08-17, HTA 2027-11-15)</t>
         </is>
       </c>
     </row>
@@ -6447,22 +6447,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>May 2028</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Dec 2028</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+          <t>Aug 2027</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Apr 2028</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2027-10-04, HTA 2028-09-12)</t>
+          <t>Spain SoC = max(guideline 2026-08-17, HTA 2027-08-25)</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
@@ -6504,12 +6504,12 @@
           <t>Dec 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -6638,7 +6638,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
@@ -6648,12 +6648,12 @@
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6685,7 +6685,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
@@ -6695,7 +6695,7 @@
           <t>Jun 2025</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Jun 2025</t>
         </is>
@@ -6732,7 +6732,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
@@ -6742,7 +6742,7 @@
           <t>Jun 2026</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Jun 2026</t>
         </is>
@@ -6779,7 +6779,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -6789,12 +6789,12 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6822,7 +6822,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -6832,12 +6832,12 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6869,7 +6869,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -6879,12 +6879,12 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6912,7 +6912,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -6922,12 +6922,12 @@
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6955,7 +6955,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
@@ -6965,12 +6965,12 @@
           <t>Dec 2026</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Feb 2027</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7002,7 +7002,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
@@ -7012,12 +7012,12 @@
           <t>Apr 2027</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Sep 2027</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7049,7 +7049,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7059,7 +7059,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7096,7 +7096,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7106,7 +7106,7 @@
           <t>Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Jan 2026</t>
         </is>
@@ -7139,34 +7139,34 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -7186,34 +7186,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -7233,34 +7233,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -7280,34 +7280,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -7327,34 +7327,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
@@ -7384,12 +7384,12 @@
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7421,7 +7421,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Nov 2026</t>
         </is>
@@ -7431,12 +7431,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7468,7 +7468,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Dec 2026</t>
         </is>
@@ -7478,12 +7478,12 @@
           <t>Mar 2027</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7515,34 +7515,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 13.5 months</t>
         </is>
       </c>
     </row>
@@ -7562,34 +7562,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2027</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 23.4 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 23.4 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
@@ -7619,12 +7619,12 @@
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7656,7 +7656,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
@@ -7666,7 +7666,7 @@
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
@@ -7703,7 +7703,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
@@ -7713,12 +7713,12 @@
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7750,7 +7750,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Aug 2027</t>
         </is>
@@ -7760,12 +7760,12 @@
           <t>Feb 2028</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Sep 2028</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
+          <t>UK SoC = max(guideline 2026-04-17, HTA 2028-02-27)</t>
         </is>
       </c>
     </row>
@@ -7797,22 +7797,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
+          <t>Mar 2027</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
           <t>Jun 2027</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2027-06-04, HTA 2027-03-11)</t>
+          <t>France SoC = max(guideline 2026-04-17, HTA 2027-03-11)</t>
         </is>
       </c>
     </row>
@@ -7844,22 +7844,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Apr 2027</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Jul 2027</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2027-06-04, EMA 2026-09-01). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-04-17, EMA 2026-09-01). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -7891,22 +7891,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Dec 2027</t>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Apr 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Apr 2028</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+          <t>Jul 2027</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Oct 2027</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2027-06-04, HTA 2028-02-27)</t>
+          <t>Italy SoC = max(guideline 2026-04-17, HTA 2027-07-16)</t>
         </is>
       </c>
     </row>
@@ -7938,22 +7938,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Jan 2028</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Aug 2028</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+          <t>Apr 2027</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Dec 2027</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2027-06-04, HTA 2028-05-13)</t>
+          <t>Spain SoC = max(guideline 2026-04-17, HTA 2027-04-25)</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Apr 2027</t>
         </is>
@@ -7995,12 +7995,12 @@
           <t>Aug 2027</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Nov 2027</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8132,7 +8132,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
@@ -8142,7 +8142,7 @@
           <t>Jul 2027</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Jul 2027</t>
         </is>
@@ -8179,7 +8179,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
@@ -8189,12 +8189,12 @@
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Mar 2028</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8226,7 +8226,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
@@ -8236,12 +8236,12 @@
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -8273,7 +8273,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8283,12 +8283,12 @@
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8320,7 +8320,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8330,12 +8330,12 @@
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8367,7 +8367,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8377,12 +8377,12 @@
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8414,7 +8414,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8424,12 +8424,12 @@
           <t>Jul 2029</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8461,7 +8461,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8471,12 +8471,12 @@
           <t>Aug 2029</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Sep 2029</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8508,7 +8508,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
@@ -8518,12 +8518,12 @@
           <t>Nov 2029</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Apr 2030</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8555,7 +8555,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
@@ -8565,12 +8565,12 @@
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8602,7 +8602,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
@@ -8612,12 +8612,12 @@
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Jan 2029</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8649,34 +8649,34 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
+          <t>Nov 2028</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -8696,34 +8696,34 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
+          <t>Nov 2028</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -8743,34 +8743,34 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
+          <t>Nov 2028</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -8790,34 +8790,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
+          <t>Nov 2028</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -8837,34 +8837,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2028</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+          <t>Nov 2028</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 12.1 months post-FDA</t>
+          <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 12.1 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
@@ -8894,12 +8894,12 @@
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8931,7 +8931,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Jun 2029</t>
         </is>
@@ -8941,12 +8941,12 @@
           <t>Oct 2029</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Feb 2030</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8978,7 +8978,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Jul 2029</t>
         </is>
@@ -8988,12 +8988,12 @@
           <t>Oct 2029</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9025,34 +9025,34 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2030</t>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2029</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Sep 2030</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2030</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+          <t>Feb 2030</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>May 2030</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 13.5 months</t>
         </is>
       </c>
     </row>
@@ -9072,34 +9072,34 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2030</t>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2029</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>Mar 2031</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+          <t>Nov 2029</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2030</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 23.4 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 23.4 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
@@ -9129,12 +9129,12 @@
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9166,7 +9166,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
@@ -9176,12 +9176,12 @@
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9209,7 +9209,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
@@ -9219,12 +9219,12 @@
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Feb 2029</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9256,7 +9256,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Mar 2030</t>
         </is>
@@ -9266,12 +9266,12 @@
           <t>Sep 2030</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Apr 2031</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
+          <t>UK SoC = max(guideline 2028-11-17, HTA 2030-09-29)</t>
         </is>
       </c>
     </row>
@@ -9303,22 +9303,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Jul 2029</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
+          <t>Oct 2029</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
           <t>Jan 2030</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9330,7 +9330,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2030-01-04, HTA 2029-10-11)</t>
+          <t>France SoC = max(guideline 2028-11-17, HTA 2029-10-11)</t>
         </is>
       </c>
     </row>
@@ -9350,22 +9350,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>Nov 2029</t>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Jun 2029</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>Feb 2030</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
+          <t>Jul 2029</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>Aug 2029</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2030-01-04, EMA 2029-07-11). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2028-11-17, EMA 2029-07-11). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -9397,22 +9397,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Jul 2030</t>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Nov 2029</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Sep 2030</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Nov 2030</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
+          <t>Feb 2030</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>May 2030</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2030-01-04, HTA 2030-09-29)</t>
+          <t>Italy SoC = max(guideline 2028-11-17, HTA 2030-02-15)</t>
         </is>
       </c>
     </row>
@@ -9444,22 +9444,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Aug 2030</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Mar 2029</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Dec 2030</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>Mar 2031</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
+          <t>Nov 2029</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>Jul 2030</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2030-01-04, HTA 2030-12-14)</t>
+          <t>Spain SoC = max(guideline 2028-11-17, HTA 2029-11-25)</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Nov 2029</t>
         </is>
@@ -9501,12 +9501,12 @@
           <t>Mar 2030</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Jun 2030</t>
         </is>
       </c>
-      <c r="G34" s="10" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>AIFA (Italy) exact GU publication dates for both analogs need primary research.</t>
+          <t>AIFA (Italy) dates confirmed: Enhertu GU n.153 on 3 Jul 2023 (~5 months post-EMA); Trodelvy GU n.185 on 9 Aug 2022 (~9 months post-EMA). Sourced from gazzettaufficiale.it and aifa.gov.it.</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -10544,16 +10544,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10568,7 +10564,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>AEMPS (Spain) exact pricing/reimbursement dates for both analogs need primary research.</t>
+          <t>AEMPS (Spain) dates confirmed: Both Enhertu and Trodelvy approved by CIPM on same date, 28 Oct 2022. Sourced from Spanish Ministry of Health press release.</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -10578,7 +10574,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -10586,16 +10582,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10648,7 +10640,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>ESMO guideline exact update dates for both analogs are approximate; need verification against ESMO publications.</t>
+          <t>ESMO guideline dates confirmed: Both Enhertu and Trodelvy included in ESMO mBC CPG published 19 Oct 2021 (Annals of Oncology). This predates Enhertu FDA full approval (Aug 2022) — the guideline referenced DESTINY-Breast03 data pre-approval.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -10658,7 +10650,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -10666,16 +10658,12 @@
           <t>General</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>Requires primary research</t>
-        </is>
-      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -10986,42 +10974,42 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (14mo) — plan enrollment</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>Moderate (17mo) — plan enrollment</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Moderate (18mo) — plan enrollment</t>
+          <t>Moderate (15mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>Moderate (14mo) — plan enrollment</t>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Narrow (11mo) — prioritize now</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Q1 2030</t>
+          <t>Q4 2029</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>Extended (45mo) — flexible timing</t>
+          <t>Extended (42mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -11038,42 +11026,42 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>Moderate (17mo) — plan enrollment</t>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Narrow (11mo) — prioritize now</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>Moderate (18mo) — plan enrollment</t>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Narrow (12mo) — prioritize now</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>Moderate (14mo) — plan enrollment</t>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>Narrow (5mo) — prioritize now</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Q1 2030</t>
+          <t>Q3 2029</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>Extended (45mo) — flexible timing</t>
+          <t>Extended (39mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -11090,42 +11078,42 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Extended (25mo) — flexible timing</t>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (18mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>Extended (26mo) — flexible timing</t>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (19mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q3 2027</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>Moderate (22mo) — plan enrollment</t>
+          <t>Moderate (15mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Q3 2030</t>
+          <t>Q1 2030</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t>Extended (53mo) — flexible timing</t>
+          <t>Extended (46mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -11142,42 +11130,42 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Extended (28mo) — flexible timing</t>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (15mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Q3 2028</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>Extended (29mo) — flexible timing</t>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>Moderate (16mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>Extended (25mo) — flexible timing</t>
+          <t>Q2 2027</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>Narrow (12mo) — prioritize now</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Q4 2030</t>
+          <t>Q4 2029</t>
         </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>Extended (56mo) — flexible timing</t>
+          <t>Extended (43mo) — flexible timing</t>
         </is>
       </c>
     </row>

--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -41,7 +41,7 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -584,14 +584,14 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Enhertu (T-DXd) — 2L+ HER2+ mBC (DESTINY-Breast03)</t>
@@ -605,7 +605,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Mar 2022</t>
+          <t>15 Mar 2022</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Sep 2021</t>
+          <t>19 Sep 2021</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>5 Aug 2022</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
@@ -787,7 +787,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>24 Jan 2023</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>24 Jan 2023</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>24 Jan 2023</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>24 Jan 2023</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Jan 2023</t>
+          <t>24 Jan 2023</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>17 Feb 2023</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>1 Sep 2022</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Sep 2022</t>
+          <t>1 Sep 2022</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Oct 2023</t>
+          <t>25 Oct 2023</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>2 Feb 2023</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Feb 2023</t>
+          <t>22 Feb 2023</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>3 Jul 2023</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>28 Oct 2022</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Jun 2023</t>
+          <t>29 Jun 2023</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>15 Aug 2022</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1648,14 +1648,14 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Trodelvy (SG) — 3L+ mTNBC (ASCENT)</t>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Nov 2020</t>
+          <t>1 Nov 2020</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Sep 2020</t>
+          <t>19 Sep 2020</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>7 Apr 2021</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>10 Nov 2021</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>10 Nov 2021</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>10 Nov 2021</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Nov 2021</t>
+          <t>10 Nov 2021</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Dec 2021</t>
+          <t>15 Dec 2021</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Jul 2022</t>
+          <t>18 Jul 2022</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>1 May 2021</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>May 2021</t>
+          <t>1 May 2021</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Oct 2021</t>
+          <t>19 Oct 2021</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Jul 2023</t>
+          <t>12 Jul 2023</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>May 2022</t>
+          <t>19 May 2022</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Apr 2022</t>
+          <t>6 Apr 2022</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Aug 2022</t>
+          <t>9 Aug 2022</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>28 Oct 2022</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Oct 2022</t>
+          <t>1 Oct 2022</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Apr 2021</t>
+          <t>15 Apr 2021</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2715,14 +2715,14 @@
     <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Derived Lag Analysis (months from FDA approval)</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Milestone</t>
@@ -3552,7 +3552,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Trodelvy (SG) — 1L mTNBC (BRCA-wt, PD-L1 CPS&lt;10) (ASCENT-03)</t>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -3631,17 +3631,17 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Jul 2028</t>
+          <t>1 Jul 2028</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Jul 2028</t>
+          <t>1 Jul 2028</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Jul 2028</t>
+          <t>1 Jul 2028</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>1 Dec 2025</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>1 Dec 2025</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>1 Dec 2025</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -3725,17 +3725,17 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -3772,17 +3772,17 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>5 Apr 2027</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -3819,17 +3819,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>5 Apr 2027</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>5 Apr 2027</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>5 Apr 2027</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>2 Apr 2027</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>11 May 2027</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>29 Jul 2027</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>13 Dec 2027</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -4054,17 +4054,17 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>18 Jul 2026</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -4195,17 +4195,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>18 Jul 2026</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>18 Jul 2026</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -4289,17 +4289,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>18 Jul 2026</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Nov 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>18 Jul 2026</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -4383,17 +4383,17 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>22 Nov 2027</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
+          <t>29 May 2028</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>6 Dec 2028</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -4430,17 +4430,17 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>27 Feb 2027</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>23 Jun 2027</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>13 Oct 2027</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -4477,17 +4477,17 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>11 Jun 2027</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
+          <t>1 Sep 2027</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>29 Jul 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>16 Oct 2027</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>4 Jan 2028</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -4571,17 +4571,17 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>25 Nov 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>23 Mar 2028</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>10 Nov 2027</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>24 Feb 2028</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -4665,17 +4665,17 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>22 Nov 2027</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>May 2028</t>
+          <t>29 May 2028</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Dec 2028</t>
+          <t>6 Dec 2028</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>11 Jun 2027</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
+          <t>1 Sep 2027</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -4853,17 +4853,17 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>18 Feb 2027</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>5 Apr 2027</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>29 Jul 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>16 Oct 2027</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>4 Jan 2028</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>25 Nov 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>23 Mar 2028</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>10 Nov 2027</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>24 Feb 2028</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -5058,7 +5058,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Trodelvy (SG) + Keytruda — 1L mTNBC (PD-L1 CPS&gt;=10) (ASCENT-04)</t>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -5137,17 +5137,17 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>1 Feb 2027</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>1 Feb 2027</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>1 Feb 2027</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>21 Jan 2026</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Oct 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -5278,17 +5278,17 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>10 Apr 2027</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>5 May 2027</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>10 Apr 2027</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>5 May 2027</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>10 Apr 2027</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>5 May 2027</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -5419,17 +5419,17 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>10 Apr 2027</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>5 May 2027</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -5466,17 +5466,17 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>2 May 2027</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>10 Jun 2027</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>28 Aug 2027</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Jan 2028</t>
+          <t>12 Jan 2028</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -5607,17 +5607,17 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -5697,17 +5697,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -5744,17 +5744,17 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -5791,17 +5791,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Dec 2025</t>
+          <t>16 Dec 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>17 Aug 2026</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>13 Apr 2027</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -5885,17 +5885,17 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>22 Dec 2027</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>28 Jun 2028</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>5 Jan 2029</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -5932,17 +5932,17 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>29 Mar 2027</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>23 Jul 2027</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>12 Nov 2027</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>19 Apr 2027</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>11 Jul 2027</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>1 Oct 2027</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -6026,17 +6026,17 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>28 Aug 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>15 Nov 2027</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>3 Feb 2028</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -6073,17 +6073,17 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>25 Dec 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Apr 2028</t>
+          <t>22 Apr 2028</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -6120,17 +6120,17 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>10 Dec 2027</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>25 Mar 2028</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -6167,17 +6167,17 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -6214,17 +6214,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>1 Nov 2026</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>22 Dec 2027</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Jun 2028</t>
+          <t>28 Jun 2028</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>5 Jan 2029</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -6308,17 +6308,17 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>19 Apr 2027</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>11 Jul 2027</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>1 Oct 2027</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -6355,17 +6355,17 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>10 Apr 2027</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>May 2027</t>
+          <t>5 May 2027</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>28 Aug 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>15 Nov 2027</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>3 Feb 2028</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>25 Dec 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Apr 2028</t>
+          <t>22 Apr 2028</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -6496,17 +6496,17 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>10 Dec 2027</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>25 Mar 2028</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dato-DXd (Datroway) — 1L mTNBC (BRCA-wt, PD-L1 CPS&lt;10) (TROPION-Breast02)</t>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -6640,17 +6640,17 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Mar 2025</t>
+          <t>1 Mar 2025</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Mar 2025</t>
+          <t>1 Mar 2025</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Mar 2025</t>
+          <t>1 Mar 2025</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -6687,17 +6687,17 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Jun 2025</t>
+          <t>1 Jun 2025</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Jun 2025</t>
+          <t>1 Jun 2025</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Jun 2025</t>
+          <t>1 Jun 2025</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -6734,17 +6734,17 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Jun 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -6824,17 +6824,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -6871,17 +6871,17 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -6914,17 +6914,17 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -6957,17 +6957,17 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>18 Nov 2026</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>31 Dec 2026</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Feb 2027</t>
+          <t>8 Feb 2027</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>28 Apr 2027</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Sep 2027</t>
+          <t>12 Sep 2027</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -7098,17 +7098,17 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>15 Jan 2026</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -7141,17 +7141,17 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>16 Aug 2025</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>16 Aug 2025</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -7235,17 +7235,17 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>16 Aug 2025</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -7282,17 +7282,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>16 Aug 2025</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -7329,17 +7329,17 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
+          <t>16 Aug 2025</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Apr 2026</t>
+          <t>17 Apr 2026</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>22 Aug 2027</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>27 Feb 2028</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>5 Sep 2028</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -7423,17 +7423,17 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Nov 2026</t>
+          <t>27 Nov 2026</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>23 Mar 2027</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>13 Jul 2027</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -7470,17 +7470,17 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>18 Dec 2026</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>1 Jun 2027</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -7517,17 +7517,17 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>28 Apr 2027</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>16 Jul 2027</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>4 Oct 2027</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -7564,17 +7564,17 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>22 Dec 2027</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>10 Aug 2027</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>24 Nov 2027</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -7658,17 +7658,17 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
@@ -7705,17 +7705,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>1 Jul 2026</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -7752,17 +7752,17 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>22 Aug 2027</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Feb 2028</t>
+          <t>27 Feb 2028</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Sep 2028</t>
+          <t>5 Sep 2028</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>18 Dec 2026</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Mar 2027</t>
+          <t>11 Mar 2027</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Jun 2027</t>
+          <t>1 Jun 2027</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -7846,17 +7846,17 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Dec 2026</t>
+          <t>12 Dec 2026</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -7893,17 +7893,17 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>28 Apr 2027</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>16 Jul 2027</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Oct 2027</t>
+          <t>4 Oct 2027</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Dec 2027</t>
+          <t>22 Dec 2027</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -7987,17 +7987,17 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Apr 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Aug 2027</t>
+          <t>10 Aug 2027</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Nov 2027</t>
+          <t>24 Nov 2027</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -8055,7 +8055,7 @@
     <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Dato-DXd (Datroway) +/- Durvalumab — 1L mTNBC (PD-L1 CPS&gt;=10) (TROPION-Breast05)</t>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Category</t>
@@ -8134,17 +8134,17 @@
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>28 Jul 2027</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>28 Jul 2027</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Jul 2027</t>
+          <t>28 Jul 2027</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -8181,17 +8181,17 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>1 Mar 2028</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>1 Mar 2028</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>1 Mar 2028</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -8228,17 +8228,17 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -8275,17 +8275,17 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>11 Jul 2029</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>5 Aug 2029</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -8322,17 +8322,17 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>11 Jul 2029</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>5 Aug 2029</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -8369,17 +8369,17 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>11 Jul 2029</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>5 Aug 2029</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>11 Jul 2029</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>5 Aug 2029</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
@@ -8463,17 +8463,17 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>2 Aug 2029</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Sep 2029</t>
+          <t>10 Sep 2029</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -8510,17 +8510,17 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>28 Nov 2029</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Apr 2030</t>
+          <t>14 Apr 2030</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -8557,17 +8557,17 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>25 Jan 2029</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>28 Jan 2029</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>28 Jan 2029</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -8604,17 +8604,17 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>25 Jan 2029</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>28 Jan 2029</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Jan 2029</t>
+          <t>28 Jan 2029</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -8651,17 +8651,17 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>18 Mar 2028</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>17 Nov 2028</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -8698,17 +8698,17 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>18 Mar 2028</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>17 Nov 2028</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -8745,17 +8745,17 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>18 Mar 2028</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>17 Nov 2028</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>18 Mar 2028</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>17 Nov 2028</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -8839,17 +8839,17 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>Mar 2028</t>
+          <t>18 Mar 2028</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Nov 2028</t>
+          <t>17 Nov 2028</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>14 Jul 2029</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -8886,17 +8886,17 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>24 Mar 2030</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Sep 2030</t>
+          <t>29 Sep 2030</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Apr 2031</t>
+          <t>8 Apr 2031</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -8933,17 +8933,17 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>29 Jun 2029</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Oct 2029</t>
+          <t>23 Oct 2029</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Feb 2030</t>
+          <t>12 Feb 2030</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -8980,17 +8980,17 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>20 Jul 2029</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Oct 2029</t>
+          <t>11 Oct 2029</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
+          <t>1 Jan 2030</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
@@ -9027,17 +9027,17 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>28 Nov 2029</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Feb 2030</t>
+          <t>15 Feb 2030</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>May 2030</t>
+          <t>6 May 2030</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -9074,17 +9074,17 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Mar 2029</t>
+          <t>27 Mar 2029</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Jul 2030</t>
+          <t>24 Jul 2030</t>
         </is>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>12 Mar 2030</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Jun 2030</t>
+          <t>26 Jun 2030</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -9168,17 +9168,17 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -9211,17 +9211,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Feb 2029</t>
+          <t>1 Feb 2029</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>24 Mar 2030</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Sep 2030</t>
+          <t>29 Sep 2030</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Apr 2031</t>
+          <t>8 Apr 2031</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>20 Jul 2029</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Oct 2029</t>
+          <t>11 Oct 2029</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Jan 2030</t>
+          <t>1 Jan 2030</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -9352,17 +9352,17 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Jun 2029</t>
+          <t>20 Jun 2029</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Jul 2029</t>
+          <t>11 Jul 2029</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Aug 2029</t>
+          <t>5 Aug 2029</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -9399,17 +9399,17 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>28 Nov 2029</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Feb 2030</t>
+          <t>15 Feb 2030</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>May 2030</t>
+          <t>6 May 2030</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -9446,17 +9446,17 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Mar 2029</t>
+          <t>27 Mar 2029</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Jul 2030</t>
+          <t>24 Jul 2030</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -9493,17 +9493,17 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>Nov 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Mar 2030</t>
+          <t>12 Mar 2030</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Jun 2030</t>
+          <t>26 Jun 2030</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -9552,14 +9552,14 @@
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Assumptions &amp; Data Gaps Log</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>ID</t>
@@ -10769,7 +10769,7 @@
     <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Corcept Phase 3 Enrollment Implications</t>
@@ -10805,7 +10805,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Geography</t>

--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -24,7 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -153,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -164,6 +166,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -181,19 +186,28 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -668,22 +682,20 @@
           <t>15 Mar 2022</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-4.7</t>
-        </is>
+      <c r="E5" s="6" t="n">
+        <v>-4.7</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT03529110</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>DESTINY-Breast03 primary analysis cutoff</t>
         </is>
@@ -710,22 +722,20 @@
           <t>19 Sep 2021</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-10.5</t>
-        </is>
+      <c r="E6" s="6" t="n">
+        <v>-10.5</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>ESMO 2021 presentation</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>First presentation at ESMO Congress 2021</t>
         </is>
@@ -758,12 +768,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Full approval for 2L+ HER2+ mBC based on DESTINY-Breast03</t>
         </is>
@@ -790,22 +800,20 @@
           <t>24 Jan 2023</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="E8" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>EMA centralized procedure; EC marketing authorization</t>
         </is>
@@ -832,22 +840,20 @@
           <t>24 Jan 2023</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="E9" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Same EMA approval applies to all EU5</t>
         </is>
@@ -874,22 +880,20 @@
           <t>24 Jan 2023</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="E10" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -912,22 +916,20 @@
           <t>24 Jan 2023</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="E11" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -950,22 +952,20 @@
           <t>24 Jan 2023</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
+      <c r="E12" s="6" t="n">
+        <v>5.6</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>MHRA GBR reliance procedure</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>MHRA followed EMA timeline via reliance pathway</t>
         </is>
@@ -992,22 +992,20 @@
           <t>17 Feb 2023</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E13" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1025,27 +1023,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>1 Sep 2022</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+      <c r="E14" s="6" t="n">
+        <v>0.9</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Category 1 preferred within ~1 month of FDA approval</t>
         </is>
@@ -1067,27 +1063,25 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>1 Sep 2022</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
+      <c r="E15" s="6" t="n">
+        <v>0.9</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -1114,22 +1108,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
+      <c r="E16" s="6" t="n">
+        <v>-9.5</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>T-DXd recommended as new standard 2L therapy for HER2+ mBC. Living Guideline format launched 11 May 2023.</t>
         </is>
@@ -1156,22 +1148,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
+      <c r="E17" s="6" t="n">
+        <v>-9.5</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1194,22 +1184,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
+      <c r="E18" s="6" t="n">
+        <v>-9.5</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1232,22 +1220,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
+      <c r="E19" s="6" t="n">
+        <v>-9.5</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1270,22 +1256,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
+      <c r="E20" s="6" t="n">
+        <v>-9.5</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1308,22 +1292,20 @@
           <t>25 Oct 2023</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
+      <c r="E21" s="6" t="n">
+        <v>14.7</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>NICE TA942</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Recommended for routine commissioning</t>
         </is>
@@ -1350,22 +1332,20 @@
           <t>2 Feb 2023</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
+      <c r="E22" s="6" t="n">
+        <v>5.9</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>G-BA Beschluss — procedure 2022-08-01-D-836</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Considerable additional benefit. Decision 9 days after EMA approval.</t>
         </is>
@@ -1392,22 +1372,20 @@
           <t>22 Feb 2023</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
+      <c r="E23" s="6" t="n">
+        <v>6.6</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>HAS CT opinion — ENHERTU_22022023_AVIS_CT19944</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>SMR: Important; ASMR III (moderate improvement). Published online 30 Mar 2023.</t>
         </is>
@@ -1434,22 +1412,20 @@
           <t>3 Jul 2023</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
+      <c r="E24" s="6" t="n">
+        <v>10.9</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>AIFA — GU Serie Generale n.153, 3 Jul 2023</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>SSN reimbursement effective 4 Jul 2023. ~5 months post-EMA — faster than typical due to innovative drug status.</t>
         </is>
@@ -1476,22 +1452,20 @@
           <t>28 Oct 2022</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
+      <c r="E25" s="6" t="n">
+        <v>2.8</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>CIPM financing decision — 28 Oct 2022</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>SNS prescription available ~Dec 2022. Based on earlier EMA type II variation (Mar 2022), not Jan 2023 broadened indication.</t>
         </is>
@@ -1513,27 +1487,25 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>29 Jun 2023</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
+      <c r="E26" s="6" t="n">
+        <v>10.8</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Recommended for reimbursement with clinical criteria</t>
         </is>
@@ -1555,27 +1527,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>15 Aug 2022</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E27" s="6" t="n">
+        <v>0.3</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Daiichi Sankyo press release</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>US commercial launch within days of FDA approval</t>
         </is>
@@ -1597,7 +1567,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -1727,27 +1697,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>1 Nov 2020</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>-5.2</t>
-        </is>
+      <c r="E5" s="6" t="n">
+        <v>-5.2</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT02574455</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>ASCENT trial primary completion</t>
         </is>
@@ -1774,22 +1742,20 @@
           <t>19 Sep 2020</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>-6.6</t>
-        </is>
+      <c r="E6" s="6" t="n">
+        <v>-6.6</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>ESMO 2020 — NEJM publication</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Primary results presented at ESMO Virtual 2020</t>
         </is>
@@ -1822,12 +1788,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>FDA approval letter</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Regular approval for 3L+ mTNBC (accelerated approval Apr 2020 converted)</t>
         </is>
@@ -1854,22 +1820,20 @@
           <t>10 Nov 2021</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="E8" s="6" t="n">
+        <v>7.1</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>EMA centralized procedure; ~7 months post-FDA</t>
         </is>
@@ -1896,22 +1860,20 @@
           <t>10 Nov 2021</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="E9" s="6" t="n">
+        <v>7.1</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1934,22 +1896,20 @@
           <t>10 Nov 2021</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="E10" s="6" t="n">
+        <v>7.1</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1972,22 +1932,20 @@
           <t>10 Nov 2021</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
+      <c r="E11" s="6" t="n">
+        <v>7.1</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2005,27 +1963,25 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>15 Dec 2021</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
+      <c r="E12" s="6" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>MHRA approval</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>MHRA followed shortly after EMA; approximate date</t>
         </is>
@@ -2052,22 +2008,20 @@
           <t>18 Jul 2022</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
+      <c r="E13" s="6" t="n">
+        <v>15.4</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Health Canada NOC</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>~15 months post-FDA</t>
         </is>
@@ -2089,27 +2043,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>1 May 2021</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="E14" s="6" t="n">
+        <v>0.8</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Added within one update cycle of full approval</t>
         </is>
@@ -2131,27 +2083,25 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>1 May 2021</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="E15" s="6" t="n">
+        <v>0.8</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2174,22 +2124,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E16" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>SG recommended as preferred treatment after anthracyclines and taxanes for mTNBC.</t>
         </is>
@@ -2216,22 +2164,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E17" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2254,22 +2200,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E18" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2292,22 +2236,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E19" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2330,22 +2272,20 @@
           <t>19 Oct 2021</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
+      <c r="E20" s="6" t="n">
+        <v>6.4</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>ESMO CPG — Annals of Oncology, 19 Oct 2021</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2368,22 +2308,20 @@
           <t>12 Jul 2023</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>27.2</t>
-        </is>
+      <c r="E21" s="6" t="n">
+        <v>27.2</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>NICE TA900</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Recommended via Cancer Drugs Fund; ~27 months post-FDA</t>
         </is>
@@ -2410,22 +2348,20 @@
           <t>19 May 2022</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
+      <c r="E22" s="6" t="n">
+        <v>13.4</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>G-BA Beschluss — procedure 2021-12-01-D-750</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>~6 months post-EMA approval.</t>
         </is>
@@ -2452,22 +2388,20 @@
           <t>6 Apr 2022</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
+      <c r="E23" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>HAS CT opinion — TRODELVY_06042022_AVIS_CT19684</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>SMR: Important; ASMR III (moderate improvement). Published online 2 Jun 2022.</t>
         </is>
@@ -2494,22 +2428,20 @@
           <t>9 Aug 2022</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
+      <c r="E24" s="6" t="n">
+        <v>16.1</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>AIFA — GU Serie Generale n.185, 9 Aug 2022</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>SSN reimbursement effective 10 Aug 2022. Access via Fund for Innovative Drugs. ~9 months post-EMA.</t>
         </is>
@@ -2536,22 +2468,20 @@
           <t>28 Oct 2022</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
+      <c r="E25" s="6" t="n">
+        <v>18.7</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Known</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>CIPM financing decision — 28 Oct 2022</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Same CIPM session approved both Trodelvy and Enhertu. SNS prescription available ~Dec 2022. ~12 months post-EMA.</t>
         </is>
@@ -2573,27 +2503,25 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>1 Oct 2022</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
+      <c r="E26" s="6" t="n">
+        <v>17.8</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>CADTH pCODR recommendation</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Approximate date; ~18 months post-FDA</t>
         </is>
@@ -2615,27 +2543,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>15 Apr 2021</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E27" s="6" t="n">
+        <v>0.3</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>Gilead press release</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>US launch shortly after FDA approval</t>
         </is>
@@ -2657,7 +2583,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2775,32 +2701,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="C4" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2813,32 +2729,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="C5" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2851,32 +2757,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="C6" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2889,32 +2785,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="C7" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2927,32 +2813,22 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="C8" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2965,32 +2841,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="C9" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -3003,32 +2869,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="C10" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -3041,32 +2897,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="C11" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3079,32 +2925,22 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="C12" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3117,32 +2953,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="C13" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3155,32 +2981,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="C14" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3193,32 +3009,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="C15" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3231,32 +3037,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="C16" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3269,32 +3065,22 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>27.2</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>14.7</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>27.2</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="C17" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3307,32 +3093,22 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="C18" s="12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3345,32 +3121,22 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="C19" s="12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3383,32 +3149,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="C20" s="12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3421,32 +3177,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
-        <is>
-          <t>18.7</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="C21" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3459,32 +3205,22 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>17.8</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="C22" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3497,32 +3233,22 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="C23" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3582,7 +3308,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -3592,7 +3318,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -3629,17 +3355,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>1 Jul 2028</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>1 Jul 2028</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>1 Jul 2028</t>
         </is>
@@ -3649,12 +3375,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT05382299 — registered PCD</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Registered PCD Jul 2028 is for final OS analysis. PFS interim already read out.</t>
         </is>
@@ -3676,32 +3402,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>1 Dec 2025</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>1 Dec 2025</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>1 Dec 2025</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Gilead presentations / regulatory submission</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>PFS data already presented; supports sBLA filing. Trial status: Active, Not Recruiting (623 enrolled).</t>
         </is>
@@ -3723,32 +3449,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated 1L launch H2 2026</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Assumes standard sBLA review (~6-8 months) or Priority Review (~6 months)</t>
         </is>
@@ -3770,32 +3496,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>5 Apr 2027</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3817,32 +3543,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>5 Apr 2027</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3864,32 +3590,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>5 Apr 2027</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3911,32 +3637,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>5 Apr 2027</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
         </is>
@@ -3958,32 +3684,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>2 Apr 2027</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>11 May 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 7.0 months</t>
         </is>
@@ -4005,32 +3731,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>29 Jul 2027</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>13 Dec 2027</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 10.9 months</t>
         </is>
@@ -4052,17 +3778,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -4072,12 +3798,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Category 1 preferred 1L mTNBC BRCA-wt/PD-L1 CPS&lt;10 — listed AHEAD of approval</t>
         </is>
@@ -4099,17 +3825,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -4119,12 +3845,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>NCCN also referenced in Canadian practice</t>
         </is>
@@ -4146,32 +3872,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>16 Nov 2025</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>18 Jul 2026</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
@@ -4193,32 +3919,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>16 Nov 2025</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>18 Jul 2026</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
@@ -4240,32 +3966,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>16 Nov 2025</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>18 Jul 2026</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
@@ -4287,32 +4013,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>16 Nov 2025</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>18 Jul 2026</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
@@ -4334,32 +4060,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>16 Nov 2025</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>18 Jul 2026</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
         </is>
@@ -4381,32 +4107,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>22 Nov 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>29 May 2028</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>6 Dec 2028</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
         </is>
@@ -4428,32 +4154,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>27 Feb 2027</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>23 Jun 2027</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>13 Oct 2027</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.7 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 9.7 months</t>
         </is>
@@ -4475,32 +4201,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>11 Jun 2027</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2027</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 9.3 months</t>
         </is>
@@ -4522,32 +4248,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>29 Jul 2027</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>16 Oct 2027</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>4 Jan 2028</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 13.5 months</t>
         </is>
@@ -4569,32 +4295,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>25 Nov 2026</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>26 Jul 2027</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>23 Mar 2028</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 10.8 months</t>
         </is>
@@ -4616,32 +4342,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>26 Jul 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>10 Nov 2027</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>24 Feb 2028</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-09-01 + 14.3 months</t>
         </is>
@@ -4663,32 +4389,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Targeting rapid launch post-approval</t>
         </is>
@@ -4710,32 +4436,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-10-01)</t>
         </is>
@@ -4757,32 +4483,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>22 Nov 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>29 May 2028</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>6 Dec 2028</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2026-07-18, HTA 2028-05-29)</t>
         </is>
@@ -4804,32 +4530,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>11 Jun 2027</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2027</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2026-07-18, HTA 2027-06-11)</t>
         </is>
@@ -4851,32 +4577,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>5 Apr 2027</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2026-07-18, EMA 2027-03-11). G-BA does not gate access.</t>
         </is>
@@ -4898,32 +4624,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>29 Jul 2027</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>16 Oct 2027</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>4 Jan 2028</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2026-07-18, HTA 2027-10-16)</t>
         </is>
@@ -4945,32 +4671,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>25 Nov 2026</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>26 Jul 2027</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>23 Mar 2028</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2026-07-18, HTA 2027-07-26)</t>
         </is>
@@ -4992,32 +4718,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>26 Jul 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>10 Nov 2027</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>24 Feb 2028</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-11-10)</t>
         </is>
@@ -5088,7 +4814,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -5098,7 +4824,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -5135,17 +4861,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>1 Feb 2027</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>1 Feb 2027</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>1 Feb 2027</t>
         </is>
@@ -5155,12 +4881,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT05382286 — registered PCD</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Registered PCD Feb 2027 is for final OS analysis. PFS data published NEJM 21 Jan 2026.</t>
         </is>
@@ -5182,17 +4908,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>21 Jan 2026</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>21 Jan 2026</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>21 Jan 2026</t>
         </is>
@@ -5202,12 +4928,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>NEJM publication — 21 Jan 2026</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Full ASCENT-04 PFS dataset published; supported NCCN Category 1 upgrade. Trial: Active, Not Recruiting (443 enrolled).</t>
         </is>
@@ -5229,32 +4955,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Projected based on Gilead H2 2026 launch target</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>May come slightly after ASCENT-03 monotherapy approval</t>
         </is>
@@ -5276,32 +5002,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>10 Apr 2027</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>5 May 2027</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5323,32 +5049,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>10 Apr 2027</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>5 May 2027</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5370,32 +5096,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>10 Apr 2027</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>5 May 2027</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5417,32 +5143,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>10 Apr 2027</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>5 May 2027</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
         </is>
@@ -5464,32 +5190,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>2 May 2027</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>10 Jun 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 7.0 months</t>
         </is>
@@ -5511,32 +5237,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>28 Aug 2027</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>12 Jan 2028</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 10.9 months</t>
         </is>
@@ -5558,17 +5284,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -5578,12 +5304,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Initially Category 2A preferred; upgraded to Category 1 in v2.2026</t>
         </is>
@@ -5605,17 +5331,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -5625,12 +5351,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5648,32 +5374,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>16 Dec 2025</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
@@ -5695,32 +5421,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>16 Dec 2025</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
@@ -5742,32 +5468,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>16 Dec 2025</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
@@ -5789,32 +5515,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>16 Dec 2025</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
@@ -5836,32 +5562,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>16 Dec 2025</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
         </is>
@@ -5883,32 +5609,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>22 Dec 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>28 Jun 2028</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>5 Jan 2029</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
         </is>
@@ -5930,32 +5656,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>29 Mar 2027</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>23 Jul 2027</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>12 Nov 2027</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.7 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 9.7 months</t>
         </is>
@@ -5977,32 +5703,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>19 Apr 2027</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2027</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1 Oct 2027</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 9.3 months</t>
         </is>
@@ -6024,32 +5750,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>28 Aug 2027</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>15 Nov 2027</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>3 Feb 2028</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 13.5 months</t>
         </is>
@@ -6071,32 +5797,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>25 Dec 2026</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>25 Aug 2027</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>22 Apr 2028</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 10.8 months</t>
         </is>
@@ -6118,32 +5844,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>25 Aug 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>10 Dec 2027</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>25 Mar 2028</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-10-01 + 14.3 months</t>
         </is>
@@ -6165,32 +5891,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Combo launch may follow monotherapy by ~1 month</t>
         </is>
@@ -6212,32 +5938,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1 Nov 2026</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-11-01)</t>
         </is>
@@ -6259,32 +5985,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>22 Dec 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>28 Jun 2028</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>5 Jan 2029</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2026-08-17, HTA 2028-06-28)</t>
         </is>
@@ -6306,32 +6032,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>19 Apr 2027</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2027</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1 Oct 2027</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2026-08-17, HTA 2027-07-11)</t>
         </is>
@@ -6353,32 +6079,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>20 Mar 2027</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>10 Apr 2027</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>5 May 2027</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2026-08-17, EMA 2027-04-10). G-BA does not gate access.</t>
         </is>
@@ -6400,32 +6126,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>28 Aug 2027</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>15 Nov 2027</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>3 Feb 2028</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2026-08-17, HTA 2027-11-15)</t>
         </is>
@@ -6447,32 +6173,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>25 Dec 2026</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>25 Aug 2027</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>22 Apr 2028</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2026-08-17, HTA 2027-08-25)</t>
         </is>
@@ -6494,32 +6220,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>25 Aug 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>10 Dec 2027</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>25 Mar 2028</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-12-10)</t>
         </is>
@@ -6591,7 +6317,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -6601,7 +6327,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -6638,32 +6364,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>1 Mar 2025</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>1 Mar 2025</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>1 Mar 2025</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT05104866 (estimated)</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>TROPION-Breast02 primary completion estimate</t>
         </is>
@@ -6685,32 +6411,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>1 Jun 2025</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>1 Jun 2025</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>1 Jun 2025</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Data presented at major congress</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Primary data supported sBLA submission</t>
         </is>
@@ -6732,32 +6458,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>1 Jun 2026</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>1 Jun 2026</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>1 Jun 2026</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>PDUFA Q2 2026 under Priority Review</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Priority Review granted Feb 2026; PDUFA target date Q2 2026</t>
         </is>
@@ -6779,32 +6505,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6822,32 +6548,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Based on regulatory submission accepted Dec 2025</t>
         </is>
@@ -6869,32 +6595,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6912,32 +6638,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6955,32 +6681,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>18 Nov 2026</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>31 Dec 2026</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>8 Feb 2027</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 7.0 months</t>
         </is>
@@ -7002,32 +6728,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>28 Apr 2027</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>12 Sep 2027</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 10.9 months</t>
         </is>
@@ -7049,17 +6775,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -7069,12 +6795,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Category 2A other recommended; upgraded to Category 2A preferred in v2.2026</t>
         </is>
@@ -7096,17 +6822,17 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>15 Jan 2026</t>
         </is>
@@ -7116,12 +6842,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7139,32 +6865,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>16 Aug 2025</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>17 Apr 2026</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
@@ -7186,32 +6912,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>16 Aug 2025</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>17 Apr 2026</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
@@ -7233,32 +6959,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>16 Aug 2025</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>17 Apr 2026</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
@@ -7280,32 +7006,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>16 Aug 2025</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>17 Apr 2026</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
@@ -7327,32 +7053,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>16 Aug 2025</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>17 Apr 2026</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
         </is>
@@ -7374,32 +7100,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>22 Aug 2027</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>27 Feb 2028</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>5 Sep 2028</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
         </is>
@@ -7421,32 +7147,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>27 Nov 2026</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>23 Mar 2027</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>13 Jul 2027</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.7 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 9.7 months</t>
         </is>
@@ -7468,32 +7194,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>18 Dec 2026</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1 Jun 2027</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 9.3 months</t>
         </is>
@@ -7515,32 +7241,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>28 Apr 2027</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>16 Jul 2027</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>4 Oct 2027</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 13.5 months</t>
         </is>
@@ -7562,32 +7288,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>25 Aug 2026</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>25 Apr 2027</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>22 Dec 2027</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 10.8 months</t>
         </is>
@@ -7609,32 +7335,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>25 Apr 2027</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>10 Aug 2027</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>24 Nov 2027</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2026-06-01 + 14.3 months</t>
         </is>
@@ -7656,32 +7382,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Projected post-PDUFA</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Expected rapid US launch following FDA approval</t>
         </is>
@@ -7703,32 +7429,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1 Jul 2026</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2026-01-15, launch 2026-07-01)</t>
         </is>
@@ -7750,32 +7476,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>22 Aug 2027</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>27 Feb 2028</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>5 Sep 2028</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2026-04-17, HTA 2028-02-27)</t>
         </is>
@@ -7797,32 +7523,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>18 Dec 2026</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>11 Mar 2027</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1 Jun 2027</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2026-04-17, HTA 2027-03-11)</t>
         </is>
@@ -7844,32 +7570,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2026-04-17, EMA 2026-09-01). G-BA does not gate access.</t>
         </is>
@@ -7891,32 +7617,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>28 Apr 2027</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>16 Jul 2027</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>4 Oct 2027</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2026-04-17, HTA 2027-07-16)</t>
         </is>
@@ -7938,32 +7664,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>25 Aug 2026</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>25 Apr 2027</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>22 Dec 2027</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2026-04-17, HTA 2027-04-25)</t>
         </is>
@@ -7985,32 +7711,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>25 Apr 2027</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>10 Aug 2027</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>24 Nov 2027</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-08-10)</t>
         </is>
@@ -8085,7 +7811,7 @@
           <t>Geography</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Optimistic</t>
         </is>
@@ -8095,7 +7821,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Conservative</t>
         </is>
@@ -8132,17 +7858,17 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>28 Jul 2027</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>28 Jul 2027</t>
         </is>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>28 Jul 2027</t>
         </is>
@@ -8152,12 +7878,12 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ClinicalTrials.gov NCT06103864 — registered PCD</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>TROPION-Breast05. Status: Recruiting. Study completion: Sep 2030.</t>
         </is>
@@ -8179,32 +7905,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>1 Mar 2028</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>1 Mar 2028</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>1 Mar 2028</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Estimated: ~5 months post-PCD for major congress presentation</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Assumes data maturation + congress cycle</t>
         </is>
@@ -8226,32 +7952,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>1 Jan 2029</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>1 Jan 2029</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>1 Jan 2029</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Projected: ~6-10 months post-submission</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Assumes standard or Priority Review</t>
         </is>
@@ -8273,32 +7999,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2029</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>5 Aug 2029</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8320,32 +8046,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2029</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>5 Aug 2029</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8367,32 +8093,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2029</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>5 Aug 2029</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8414,32 +8140,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2029</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>5 Aug 2029</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 6.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
         </is>
@@ -8461,32 +8187,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>2 Aug 2029</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>10 Sep 2029</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 7.0 months post-FDA</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 7.0 months</t>
         </is>
@@ -8508,32 +8234,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>28 Nov 2029</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>14 Apr 2030</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 10.9 months</t>
         </is>
@@ -8555,32 +8281,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>25 Jan 2029</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>28 Jan 2029</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>28 Jan 2029</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8602,32 +8328,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>25 Jan 2029</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>28 Jan 2029</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>28 Jan 2029</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 0.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
         </is>
@@ -8649,32 +8375,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>18 Mar 2028</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>17 Nov 2028</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
@@ -8696,32 +8422,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>18 Mar 2028</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>17 Nov 2028</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
@@ -8743,32 +8469,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>18 Mar 2028</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>17 Nov 2028</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
@@ -8790,32 +8516,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>18 Mar 2028</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>17 Nov 2028</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
@@ -8837,32 +8563,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>18 Mar 2028</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>17 Nov 2028</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): -1.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
         </is>
@@ -8884,32 +8610,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>24 Mar 2030</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>29 Sep 2030</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>8 Apr 2031</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 20.9 months post-FDA</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
         </is>
@@ -8931,32 +8657,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>29 Jun 2029</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>23 Oct 2029</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>12 Feb 2030</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.7 months post-FDA</t>
         </is>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 9.7 months</t>
         </is>
@@ -8978,32 +8704,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>20 Jul 2029</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>11 Oct 2029</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>1 Jan 2030</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 9.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 9.3 months</t>
         </is>
@@ -9025,32 +8751,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t>28 Nov 2029</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>15 Feb 2030</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>6 May 2030</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 13.5 months post-FDA</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 13.5 months</t>
         </is>
@@ -9072,32 +8798,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>27 Mar 2029</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>25 Nov 2029</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>24 Jul 2030</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 10.8 months</t>
         </is>
@@ -9119,32 +8845,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>25 Nov 2029</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>12 Mar 2030</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>26 Jun 2030</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Analog-based projection (base): 14.3 months post-FDA</t>
         </is>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Projected from FDA approval 2029-01-01 + 14.3 months</t>
         </is>
@@ -9166,32 +8892,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="18" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="F27" s="12" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Projected post-FDA approval</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -9209,32 +8935,32 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="18" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>1 Feb 2029</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>US SoC = max(NCCN 2029-01-28, launch 2029-02-01)</t>
         </is>
@@ -9256,32 +8982,32 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>24 Mar 2030</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="18" t="inlineStr">
         <is>
           <t>29 Sep 2030</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>8 Apr 2031</t>
         </is>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>UK SoC = max(guideline 2028-11-17, HTA 2030-09-29)</t>
         </is>
@@ -9303,32 +9029,32 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>20 Jul 2029</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>11 Oct 2029</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>1 Jan 2030</t>
         </is>
       </c>
-      <c r="G30" s="12" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>France SoC = max(guideline 2028-11-17, HTA 2029-10-11)</t>
         </is>
@@ -9350,32 +9076,32 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>20 Jun 2029</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>11 Jul 2029</t>
         </is>
       </c>
-      <c r="F31" s="12" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>5 Aug 2029</t>
         </is>
       </c>
-      <c r="G31" s="12" t="inlineStr">
+      <c r="G31" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>DE SoC = max(ESMO 2028-11-17, EMA 2029-07-11). G-BA does not gate access.</t>
         </is>
@@ -9397,32 +9123,32 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>28 Nov 2029</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="18" t="inlineStr">
         <is>
           <t>15 Feb 2030</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>6 May 2030</t>
         </is>
       </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="G32" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="H32" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Italy SoC = max(guideline 2028-11-17, HTA 2030-02-15)</t>
         </is>
@@ -9444,32 +9170,32 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>27 Mar 2029</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="18" t="inlineStr">
         <is>
           <t>25 Nov 2029</t>
         </is>
       </c>
-      <c r="F33" s="12" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>24 Jul 2030</t>
         </is>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G33" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Spain SoC = max(guideline 2028-11-17, HTA 2029-11-25)</t>
         </is>
@@ -9491,32 +9217,32 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>25 Nov 2029</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="18" t="inlineStr">
         <is>
           <t>12 Mar 2030</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>26 Jun 2030</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G34" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>Derived: max(guideline, reimbursement/access)</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Canada SoC = max(guideline 2029-01-28, HTA 2030-03-12)</t>
         </is>
@@ -9553,7 +9279,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>Assumptions &amp; Data Gaps Log</t>
         </is>
@@ -9612,7 +9338,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>FDA approval date is used as T=0 anchor for all market-relative lag projections.</t>
         </is>
@@ -9637,7 +9363,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -9650,7 +9376,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Two analogs bracket the projection range: Enhertu 2L+ HER2+ mBC (optimistic) and Trodelvy 3L+ mTNBC (conservative).</t>
         </is>
@@ -9675,7 +9401,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -9688,7 +9414,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>SoC integration is defined as the LATER of (a) guideline inclusion and (b) national reimbursement/access.</t>
         </is>
@@ -9713,7 +9439,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -9726,7 +9452,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>For Germany, SoC integration uses EMA approval date (not G-BA) as access is available during free-pricing period under AMNOG.</t>
         </is>
@@ -9751,7 +9477,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -9764,7 +9490,7 @@
           <t>Methodology</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>For US, SoC integration = max(NCCN guideline inclusion, commercial launch date). No HTA gate.</t>
         </is>
@@ -9789,7 +9515,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9802,7 +9528,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>EMA centralized procedure assumed for all EU5 markets; no national divergence.</t>
         </is>
@@ -9827,7 +9553,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9840,7 +9566,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>MHRA assumed to follow EMA via Great Britain reliance pathway, adding 0-2 months to EMA date.</t>
         </is>
@@ -9865,7 +9591,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -9878,7 +9604,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>Health Canada assumed to run parallel review; typically 6-15 months post-FDA based on analogs.</t>
         </is>
@@ -9903,7 +9629,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -9916,7 +9642,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Dato-DXd (TROPION-Breast02) PDUFA target Q2 2026 based on FDA Priority Review grant Feb 2026.</t>
         </is>
@@ -9941,7 +9667,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -9954,7 +9680,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-03) FDA approval targeted H2 2026 based on Gilead Q4 2025 Earnings guidance for accelerated launch.</t>
         </is>
@@ -9979,7 +9705,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -9992,7 +9718,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Trodelvy 1L (ASCENT-04 combo) FDA approval expected H2 2026, possibly 1-2 months after ASCENT-03 monotherapy.</t>
         </is>
@@ -10017,7 +9743,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -10030,7 +9756,7 @@
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>Dato-DXd EU/China approval projected as early as Q3 2026 per Daiichi Q3 FY2025 Earnings guidance, based on regulatory submission accepted Dec 2025.</t>
         </is>
@@ -10055,7 +9781,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -10068,7 +9794,7 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>TROPION-Breast05 (NCT06103864) registered PCD is Jul 28, 2027. Status: Recruiting. Study completion Sep 2030. Confirmed via ClinicalTrials.gov API.</t>
         </is>
@@ -10093,7 +9819,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -10106,7 +9832,7 @@
           <t>Trial</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>ASCENT-03 (NCT05382299) registered PCD Jul 2028; ASCENT-04 (NCT05382286) registered PCD Feb 2027. Both are final OS analysis dates — PFS data already presented. Note: original NCT numbers in data were swapped, now corrected. Confirmed via ClinicalTrials.gov API.</t>
         </is>
@@ -10131,7 +9857,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -10144,7 +9870,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>NCCN already lists both Trodelvy and Dato-DXd for 1L mTNBC pre-approval (v1.2026 and v2.2026). NCCN guideline milestone is therefore BEFORE FDA approval — unusual but confirmed.</t>
         </is>
@@ -10169,7 +9895,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -10182,7 +9908,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>ESMO guideline inclusion for 1L TNBC ADCs assumed to follow within 6-12 months of FDA approval, based on analog precedent.</t>
         </is>
@@ -10207,7 +9933,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10220,7 +9946,7 @@
           <t>Guideline</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>Trodelvy Category 1 vs Dato-DXd Category 2A reflects greater evidence maturity (inc. OS data in 2L), not lack of support for Dato-DXd.</t>
         </is>
@@ -10245,7 +9971,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -10258,7 +9984,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>NICE appraisal timelines assumed 12-28 months post-FDA based on analogs. CDF route possible for Dato-DXd given weaker evidence vs Trodelvy.</t>
         </is>
@@ -10283,7 +10009,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10296,7 +10022,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>G-BA AMNOG assessment assumed within 3-6 months of EMA approval; does not gate market access in Germany.</t>
         </is>
@@ -10321,7 +10047,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10334,7 +10060,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>HAS (France) transparency committee opinion assumed 8-17 months post-FDA; pricing negotiation adds further time.</t>
         </is>
@@ -10359,7 +10085,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10372,7 +10098,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>AIFA (Italy) reimbursement assumed 18-24 months post-FDA; typically slowest EU5 market.</t>
         </is>
@@ -10397,7 +10123,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -10410,7 +10136,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>AEMPS/Spain reimbursement assumed 20-27 months post-FDA; national + regional pricing layers add variability.</t>
         </is>
@@ -10435,7 +10161,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10448,7 +10174,7 @@
           <t>Reimbursement</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>CADTH/pCODR (Canada) recommendation assumed 12-20 months post-FDA; provincial listing adds further time.</t>
         </is>
@@ -10473,7 +10199,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -10486,7 +10212,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>HAS (France) decision dates confirmed: Enhertu CT opinion 22 Feb 2023, Trodelvy CT opinion 6 Apr 2022. Sourced from has-sante.fr.</t>
         </is>
@@ -10511,7 +10237,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -10524,7 +10250,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>AIFA (Italy) dates confirmed: Enhertu GU n.153 on 3 Jul 2023 (~5 months post-EMA); Trodelvy GU n.185 on 9 Aug 2022 (~9 months post-EMA). Sourced from gazzettaufficiale.it and aifa.gov.it.</t>
         </is>
@@ -10549,7 +10275,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -10562,7 +10288,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>AEMPS (Spain) dates confirmed: Both Enhertu and Trodelvy approved by CIPM on same date, 28 Oct 2022. Sourced from Spanish Ministry of Health press release.</t>
         </is>
@@ -10587,7 +10313,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -10600,7 +10326,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>G-BA AMNOG dates confirmed: Enhertu Beschluss 2 Feb 2023 (procedure D-836), Trodelvy Beschluss 19 May 2022 (procedure D-750). Sourced from g-ba.de.</t>
         </is>
@@ -10625,7 +10351,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -10638,7 +10364,7 @@
           <t>Data Gap</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>ESMO guideline dates confirmed: Both Enhertu and Trodelvy included in ESMO mBC CPG published 19 Oct 2021 (Annals of Oncology). This predates Enhertu FDA full approval (Aug 2022) — the guideline referenced DESTINY-Breast03 data pre-approval.</t>
         </is>
@@ -10663,7 +10389,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -10676,7 +10402,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>Trodelvy's Category 1 preferred NCCN status and broader 1L population coverage (CPS&lt;10 AND CPS&gt;=10) gives it a competitive advantage over Dato-DXd at launch.</t>
         </is>
@@ -10701,7 +10427,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -10714,7 +10440,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>Both ADCs have NCCN recommendations ahead of regulatory approval — unusual precedent that may accelerate SoC integration in US.</t>
         </is>
@@ -10739,7 +10465,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10784,22 +10510,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&lt;10 (ASCENT-03)</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Trodelvy 1L CPS&gt;=10 (ASCENT-04)</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&lt;10 (TB02)</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Dato-DXd 1L CPS&gt;=10 (TB05)</t>
         </is>
@@ -10863,7 +10589,7 @@
           <t>US</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>N/A (Commercial)</t>
         </is>
@@ -10873,7 +10599,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Narrow (6mo) — prioritize now</t>
         </is>
@@ -10883,7 +10609,7 @@
           <t>Q4 2026</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Narrow (7mo) — prioritize now</t>
         </is>
@@ -10893,7 +10619,7 @@
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>Narrow (3mo) — prioritize now</t>
         </is>
@@ -10903,7 +10629,7 @@
           <t>Q1 2029</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Extended (34mo) — flexible timing</t>
         </is>
@@ -10915,7 +10641,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>NICE</t>
         </is>
@@ -10925,7 +10651,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Extended (25mo) — flexible timing</t>
         </is>
@@ -10935,7 +10661,7 @@
           <t>Q2 2028</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Extended (26mo) — flexible timing</t>
         </is>
@@ -10945,7 +10671,7 @@
           <t>Q1 2028</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr">
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>Moderate (22mo) — plan enrollment</t>
         </is>
@@ -10955,7 +10681,7 @@
           <t>Q3 2030</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Extended (53mo) — flexible timing</t>
         </is>
@@ -10967,7 +10693,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>HAS (Transparency Committee)</t>
         </is>
@@ -10977,7 +10703,7 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Moderate (14mo) — plan enrollment</t>
         </is>
@@ -10987,7 +10713,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>Moderate (15mo) — plan enrollment</t>
         </is>
@@ -10997,7 +10723,7 @@
           <t>Q1 2027</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>Narrow (11mo) — prioritize now</t>
         </is>
@@ -11007,7 +10733,7 @@
           <t>Q4 2029</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>Extended (42mo) — flexible timing</t>
         </is>
@@ -11019,7 +10745,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>G-BA (AMNOG)</t>
         </is>
@@ -11029,7 +10755,7 @@
           <t>Q1 2027</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Narrow (11mo) — prioritize now</t>
         </is>
@@ -11039,7 +10765,7 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Narrow (12mo) — prioritize now</t>
         </is>
@@ -11049,7 +10775,7 @@
           <t>Q3 2026</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>Narrow (5mo) — prioritize now</t>
         </is>
@@ -11059,7 +10785,7 @@
           <t>Q3 2029</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>Extended (39mo) — flexible timing</t>
         </is>
@@ -11071,7 +10797,7 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>AIFA</t>
         </is>
@@ -11081,7 +10807,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Moderate (18mo) — plan enrollment</t>
         </is>
@@ -11091,7 +10817,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>Moderate (19mo) — plan enrollment</t>
         </is>
@@ -11101,7 +10827,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="H9" s="20" t="inlineStr">
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>Moderate (15mo) — plan enrollment</t>
         </is>
@@ -11111,7 +10837,7 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>Extended (46mo) — flexible timing</t>
         </is>
@@ -11123,7 +10849,7 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>AEMPS / IPT</t>
         </is>
@@ -11133,7 +10859,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>Moderate (15mo) — plan enrollment</t>
         </is>
@@ -11143,7 +10869,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>Moderate (16mo) — plan enrollment</t>
         </is>
@@ -11153,7 +10879,7 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>Narrow (12mo) — prioritize now</t>
         </is>
@@ -11163,7 +10889,7 @@
           <t>Q4 2029</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>Extended (43mo) — flexible timing</t>
         </is>
@@ -11175,7 +10901,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>CADTH / pCODR</t>
         </is>
@@ -11185,7 +10911,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>Moderate (19mo) — plan enrollment</t>
         </is>
@@ -11195,7 +10921,7 @@
           <t>Q4 2027</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>Moderate (20mo) — plan enrollment</t>
         </is>
@@ -11205,7 +10931,7 @@
           <t>Q3 2027</t>
         </is>
       </c>
-      <c r="H11" s="20" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>Moderate (16mo) — plan enrollment</t>
         </is>
@@ -11215,63 +10941,63 @@
           <t>Q1 2030</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>Extended (47mo) — flexible timing</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Key Findings</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>US: NCCN already includes both Trodelvy and Dato-DXd pre-approval. SoC integration will occur at commercial launch (H2 2026).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Germany: Access available at EMA approval (free pricing period). Among earliest EU5 markets for SoC shift.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>UK: NICE CDF pathway likely for newer ADCs. Full SoC integration may lag 12-28 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>France/Italy/Spain: Longest reimbursement timelines (12-27 months post-FDA). Extended enrollment windows.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Canada: Moderate timeline. CADTH recommendation typically 12-20 months post-FDA.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Dato-DXd CPS&gt;=10 (TROPION-Breast05): Significantly behind — PCD ~Oct 2027, FDA ~2029. Extended window in all markets.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Implication: Geographies with longer HTA timelines (IT, ES, FR) offer wider pre-SoC enrollment windows for Corcept's Phase 3.</t>
         </is>

--- a/output/drug_approval_timelines.xlsx
+++ b/output/drug_approval_timelines.xlsx
@@ -90,14 +90,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -220,7 +220,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>-4.7</v>
+        <v>-1.6</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-10.5</v>
+        <v>-7.5</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ESMO 2021 presentation</t>
+          <t>ESMO 2021 presentation; published NEJM 2022</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>First presentation at ESMO Congress 2021</t>
+          <t>First presentation at ESMO Congress Sep 19 2021. Published in NEJM (DOI: 10.1056/NEJMoa2203032).</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>5 Aug 2022</t>
+          <t>4 May 2022</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
@@ -768,14 +768,14 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>FDA approval letter</t>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>FDA BLA 761139/S-013 — conversion to regular approval and 2L+ expansion</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Full approval for 2L+ HER2+ mBC based on DESTINY-Breast03</t>
+          <t>Regular approval for 2L+ HER2+ mBC (after 1+ prior anti-HER2 regimen) based on DESTINY-Breast03. Note: Aug 5, 2022 was a SEPARATE approval for HER2-low (DESTINY-Breast04).</t>
         </is>
       </c>
     </row>
@@ -795,27 +795,27 @@
           <t>France</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>24 Jan 2023</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>25 Jul 2022</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>EC decision — EMA EPAR</t>
+          <t>EC decision — EMA Type II variation II-14 (DESTINY-Breast03)</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>EMA centralized procedure; EC marketing authorization</t>
+          <t>CHMP opinion adopted, published 2 Aug 2022 per EPAR. EC decision ~Jul 2022. G-BA dossier submitted 25 Jul 2022 confirms market entry date.</t>
         </is>
       </c>
     </row>
@@ -835,27 +835,27 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>24 Jan 2023</t>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>25 Jul 2022</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>EC decision — EMA EPAR</t>
+          <t>EC decision — EMA Type II variation II-14 (DESTINY-Breast03)</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Same EMA approval applies to all EU5</t>
+          <t>Same EC decision applies to all EU5. Date confirmed by G-BA dossier submission date.</t>
         </is>
       </c>
     </row>
@@ -875,22 +875,22 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>24 Jan 2023</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>25 Jul 2022</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>EC decision — EMA EPAR</t>
+          <t>EC decision — EMA Type II variation II-14 (DESTINY-Breast03)</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
@@ -911,22 +911,22 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>24 Jan 2023</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>25 Jul 2022</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>EC decision — EMA EPAR</t>
+          <t>EC decision — EMA Type II variation II-14 (DESTINY-Breast03)</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
@@ -947,27 +947,27 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>24 Jan 2023</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>1 Sep 2022</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>MHRA GBR reliance procedure</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>MHRA approval — estimated from EMA reliance pathway</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>MHRA followed EMA timeline via reliance pathway</t>
+          <t>MHRA typically follows EMA via reliance pathway within 0-2 months. EMA variation published Aug 2022. NICE TA862 (Feb 2023) requires prior MHRA approval.</t>
         </is>
       </c>
     </row>
@@ -987,25 +987,29 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>17 Feb 2023</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Health Canada NOC</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Health Canada NOC — DPD database</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>~10 months post-FDA. Searched via Health Canada Drug Product Database (DIN lookup for trastuzumab deruxtecan).</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1029,21 +1033,21 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Category 1 preferred within ~1 month of FDA approval</t>
+          <t>Category 1 preferred within ~4 months of FDA approval. NCCN guidelines require login at nccn.org.</t>
         </is>
       </c>
     </row>
@@ -1069,21 +1073,21 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v5.2022</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>NCCN also referenced in Canadian practice</t>
+          <t>NCCN also referenced in Canadian practice.</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1113,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1123,7 +1127,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>T-DXd recommended as new standard 2L therapy for HER2+ mBC. Living Guideline format launched 11 May 2023.</t>
+          <t>T-DXd recommended as new standard 2L therapy for HER2+ mBC. Published online 19 Oct 2021; print Dec 2021 (Vol 32, Issue 12).</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1153,7 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1185,7 +1189,7 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1221,7 +1225,7 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1257,7 +1261,7 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
@@ -1289,11 +1293,11 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>25 Oct 2023</t>
+          <t>1 Feb 2023</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -1302,12 +1306,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>NICE TA942</t>
+          <t>NICE TA862</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Recommended for routine commissioning</t>
+          <t>Recommended via managed access agreement (Cancer Drugs Fund). Published 1 Feb 2023.</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1337,7 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
@@ -1347,7 +1351,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Considerable additional benefit. Decision 9 days after EMA approval.</t>
+          <t>Considerable additional benefit. Procedure started 1 Aug 2022, Beschluss 2 Feb 2023.</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1377,7 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1382,7 +1386,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>HAS CT opinion — ENHERTU_22022023_AVIS_CT19944</t>
+          <t>HAS CT opinion — 22 Feb 2023</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -1413,7 +1417,7 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>10.9</v>
+        <v>14</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>SSN reimbursement effective 4 Jul 2023. ~5 months post-EMA — faster than typical due to innovative drug status.</t>
+          <t>SSN reimbursement effective 4 Jul 2023. ~12 months post-EMA variation.</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1457,7 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>SNS prescription available ~Dec 2022. Based on earlier EMA type II variation (Mar 2022), not Jan 2023 broadened indication.</t>
+          <t>SNS prescription available ~Dec 2022. Same CIPM session approved both Enhertu and Trodelvy.</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1497,7 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Recommended for reimbursement with clinical criteria</t>
+          <t>Recommended for reimbursement with clinical criteria. ~14 months post-FDA.</t>
         </is>
       </c>
     </row>
@@ -1529,25 +1533,25 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>15 Aug 2022</t>
+          <t>15 May 2022</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Daiichi Sankyo press release</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo / AstraZeneca — rapid US launch post-approval</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>US commercial launch within days of FDA approval</t>
+          <t>US commercial launch within days of FDA approval. Source: Daiichi Sankyo corporate communications.</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1571,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -1580,27 +1584,21 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1752,12 +1750,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>ESMO 2020 — NEJM publication</t>
+          <t>NEJM — Sacituzumab Govitecan in Metastatic Triple-Negative Breast Cancer</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Primary results presented at ESMO Virtual 2020</t>
+          <t>Primary results presented at ESMO Virtual 2020. Published NEJM Apr 22 2021 (DOI: 10.1056/NEJMoa2028485).</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1788,12 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>FDA approval letter</t>
+          <t>FDA approval — regular approval for 3L+ mTNBC</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Regular approval for 3L+ mTNBC (accelerated approval Apr 2020 converted)</t>
+          <t>Regular approval for 3L+ mTNBC (accelerated approval Apr 2020 converted).</t>
         </is>
       </c>
     </row>
@@ -1817,11 +1815,11 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>10 Nov 2021</t>
+          <t>22 Nov 2021</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1835,7 +1833,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>EMA centralized procedure; ~7 months post-FDA</t>
+          <t>EMA marketing authorisation granted 22 Nov 2021 per EPAR. ~7 months post-FDA.</t>
         </is>
       </c>
     </row>
@@ -1857,11 +1855,11 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>10 Nov 2021</t>
+          <t>22 Nov 2021</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1873,7 +1871,11 @@
           <t>EC decision — EMA EPAR</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Same EC decision applies to all EU5.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1893,11 +1895,11 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>10 Nov 2021</t>
+          <t>22 Nov 2021</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1929,11 +1931,11 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>10 Nov 2021</t>
+          <t>22 Nov 2021</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -1963,7 +1965,7 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>15 Dec 2021</t>
         </is>
@@ -1973,17 +1975,17 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>MHRA approval</t>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>MHRA approval — estimated</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>MHRA followed shortly after EMA; approximate date</t>
+          <t>MHRA followed shortly after EMA (~1 month). Exact date from MHRA product database (products.mhra.gov.uk).</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2005,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>18 Jul 2022</t>
         </is>
@@ -2013,17 +2015,17 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Known</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Health Canada NOC</t>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Health Canada NOC — DPD database</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>~15 months post-FDA</t>
+          <t>~15 months post-FDA. Searched via Health Canada Drug Product Database (DIN lookup for sacituzumab govitecan).</t>
         </is>
       </c>
     </row>
@@ -2056,14 +2058,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Added within one update cycle of full approval</t>
+          <t>Added within one update cycle of full approval. NCCN guidelines require login at nccn.org.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2098,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v4.2021</t>
         </is>
@@ -2305,11 +2307,11 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>12 Jul 2023</t>
+          <t>17 Aug 2022</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>27.2</v>
+        <v>16.3</v>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
@@ -2318,12 +2320,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>NICE TA900</t>
+          <t>NICE TA819</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Recommended via Cancer Drugs Fund; ~27 months post-FDA</t>
+          <t>Recommended for 3L+ mTNBC. Published 17 Aug 2022. ~16 months post-FDA.</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2365,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>~6 months post-EMA approval.</t>
+          <t>Beschluss 19 May 2022. ~6 months post-EMA approval.</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2400,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>HAS CT opinion — TRODELVY_06042022_AVIS_CT19684</t>
+          <t>HAS CT opinion — 6 Apr 2022</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2443,7 +2445,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>SSN reimbursement effective 10 Aug 2022. Access via Fund for Innovative Drugs. ~9 months post-EMA.</t>
+          <t>SSN reimbursement effective 10 Aug 2022. Access via Innovative Medicines Fund. ~9 months post-EMA.</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2505,7 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>1 Oct 2022</t>
         </is>
@@ -2518,12 +2520,12 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>CADTH pCODR recommendation</t>
+          <t>CADTH pCODR recommendation — approximate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Approximate date; ~18 months post-FDA</t>
+          <t>~18 months post-FDA. Date approximate; sourced from CADTH database (cadth.ca/sacituzumab-govitecan).</t>
         </is>
       </c>
     </row>
@@ -2556,14 +2558,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Gilead press release</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Gilead Sciences — US launch post-FDA approval</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>US launch shortly after FDA approval</t>
+          <t>US commercial launch shortly after FDA approval. Source: Gilead corporate communications.</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2585,7 @@
           <t>All</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
@@ -2601,22 +2603,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2702,19 +2699,19 @@
         </is>
       </c>
       <c r="C4" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="G4" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H4" s="8" t="inlineStr"/>
     </row>
@@ -2730,19 +2727,19 @@
         </is>
       </c>
       <c r="C5" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="G5" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H5" s="8" t="inlineStr"/>
     </row>
@@ -2758,19 +2755,19 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="G6" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H6" s="8" t="inlineStr"/>
     </row>
@@ -2786,19 +2783,19 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
     </row>
@@ -2814,16 +2811,16 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>8.300000000000001</v>
@@ -2842,16 +2839,16 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>15.4</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="G9" s="13" t="n">
         <v>15.4</v>
@@ -2870,7 +2867,7 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>0.8</v>
@@ -2879,10 +2876,10 @@
         <v>0.8</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="H10" s="8" t="inlineStr"/>
     </row>
@@ -2898,7 +2895,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>0.8</v>
@@ -2907,10 +2904,10 @@
         <v>0.8</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="H11" s="8" t="inlineStr"/>
     </row>
@@ -2926,16 +2923,16 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="G12" s="13" t="n">
         <v>6.4</v>
@@ -2954,16 +2951,16 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>6.4</v>
@@ -2982,16 +2979,16 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="G14" s="13" t="n">
         <v>6.4</v>
@@ -3010,16 +3007,16 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="G15" s="13" t="n">
         <v>6.4</v>
@@ -3038,16 +3035,16 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>6.4</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-9.5</v>
+        <v>-6.5</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>-1.5</v>
+        <v>-0</v>
       </c>
       <c r="G16" s="13" t="n">
         <v>6.4</v>
@@ -3066,19 +3063,19 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>27.2</v>
+        <v>16.3</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>14.7</v>
+        <v>8.9</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>20.9</v>
+        <v>12.6</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>27.2</v>
+        <v>16.3</v>
       </c>
       <c r="H17" s="8" t="inlineStr"/>
     </row>
@@ -3094,16 +3091,16 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>13.4</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>5.9</v>
+        <v>8.9</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>9.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="G18" s="13" t="n">
         <v>13.4</v>
@@ -3122,16 +3119,16 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>9.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="G19" s="13" t="n">
         <v>12</v>
@@ -3150,16 +3147,16 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>10.9</v>
+        <v>14</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>16.1</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>10.9</v>
+        <v>14</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>13.5</v>
+        <v>15.1</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>16.1</v>
@@ -3178,16 +3175,16 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>18.7</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="G21" s="13" t="n">
         <v>18.7</v>
@@ -3206,16 +3203,16 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
       <c r="D22" s="13" t="n">
         <v>17.8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>10.8</v>
+        <v>13.8</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="G22" s="13" t="n">
         <v>17.8</v>
@@ -3234,7 +3231,7 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>0.3</v>
@@ -3246,7 +3243,7 @@
         <v>0.3</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
     </row>
@@ -3469,14 +3466,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated 1L launch H2 2026</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Assumes standard sBLA review (~6-8 months) or Priority Review (~6 months)</t>
+          <t>Assumes standard sBLA review (~6-8 months) or Priority Review (~6 months).</t>
         </is>
       </c>
     </row>
@@ -3498,32 +3495,32 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>22 Nov 2026</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>3 Feb 2027</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>5 Apr 2027</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+          <t>17 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -3545,32 +3542,32 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>22 Nov 2026</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>3 Feb 2027</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>5 Apr 2027</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+          <t>17 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -3592,32 +3589,32 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>22 Nov 2026</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>3 Feb 2027</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>5 Apr 2027</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+          <t>17 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -3639,32 +3636,32 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>22 Nov 2026</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>3 Feb 2027</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>5 Apr 2027</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+          <t>17 Apr 2027</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3683,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>28 Dec 2026</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -3699,19 +3696,19 @@
           <t>11 May 2027</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 7.0 months post-FDA</t>
+          <t>Analog-based projection (base): 6.1 months post-FDA</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 7.0 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 6.1 months</t>
         </is>
       </c>
     </row>
@@ -3733,12 +3730,12 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>14 Mar 2027</t>
+          <t>14 Jun 2027</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>29 Jul 2027</t>
+          <t>13 Sep 2027</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -3746,19 +3743,19 @@
           <t>13 Dec 2027</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.4 months post-FDA</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 10.9 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 12.4 months</t>
         </is>
       </c>
     </row>
@@ -3798,14 +3795,14 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Category 1 preferred 1L mTNBC BRCA-wt/PD-L1 CPS&lt;10 — listed AHEAD of approval</t>
+          <t>Category 1 preferred 1L mTNBC BRCA-wt/PD-L1 CPS&lt;10 — listed AHEAD of approval. NCCN requires login at nccn.org.</t>
         </is>
       </c>
     </row>
@@ -3845,14 +3842,14 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>NCCN also referenced in Canadian practice</t>
+          <t>NCCN also referenced in Canadian practice.</t>
         </is>
       </c>
     </row>
@@ -3874,12 +3871,12 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>16 Nov 2025</t>
+          <t>16 Feb 2026</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>18 Jul 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -3887,19 +3884,19 @@
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3918,12 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>16 Nov 2025</t>
+          <t>16 Feb 2026</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>18 Jul 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -3934,19 +3931,19 @@
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -3968,12 +3965,12 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>16 Nov 2025</t>
+          <t>16 Feb 2026</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>18 Jul 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -3981,19 +3978,19 @@
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4012,12 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>16 Nov 2025</t>
+          <t>16 Feb 2026</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>18 Jul 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
@@ -4028,19 +4025,19 @@
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4059,12 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>16 Nov 2025</t>
+          <t>16 Feb 2026</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>18 Jul 2026</t>
+          <t>1 Sep 2026</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -4075,19 +4072,19 @@
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -4109,32 +4106,32 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>22 Nov 2027</t>
+          <t>29 May 2027</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>29 May 2028</t>
+          <t>19 Sep 2027</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>6 Dec 2028</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+          <t>10 Jan 2028</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.6 months post-FDA</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 12.6 months</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4153,12 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>27 Feb 2027</t>
+          <t>29 May 2027</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>23 Jun 2027</t>
+          <t>7 Aug 2027</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -4169,19 +4166,19 @@
           <t>13 Oct 2027</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+          <t>Analog-based projection (base): 11.2 months post-FDA</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 9.7 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 11.2 months</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4200,12 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>20 Jun 2027</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>11 Jun 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -4216,19 +4213,19 @@
           <t>1 Sep 2027</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 9.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4247,12 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>29 Jul 2027</t>
+          <t>1 Nov 2027</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>16 Oct 2027</t>
+          <t>4 Dec 2027</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4263,19 +4260,19 @@
           <t>4 Jan 2028</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 13.5 months post-FDA</t>
+          <t>Analog-based projection (base): 15.1 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 13.5 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 15.1 months</t>
         </is>
       </c>
     </row>
@@ -4297,12 +4294,12 @@
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>25 Nov 2026</t>
+          <t>24 Feb 2027</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>26 Jul 2027</t>
+          <t>7 Sep 2027</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -4310,19 +4307,19 @@
           <t>23 Mar 2028</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.8 months post-FDA</t>
+          <t>Analog-based projection (base): 12.2 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 10.8 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 12.2 months</t>
         </is>
       </c>
     </row>
@@ -4344,12 +4341,12 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>26 Jul 2027</t>
+          <t>26 Oct 2027</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>10 Nov 2027</t>
+          <t>25 Dec 2027</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -4357,19 +4354,19 @@
           <t>24 Feb 2028</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 14.3 months post-FDA</t>
+          <t>Analog-based projection (base): 15.8 months post-FDA</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-09-01 + 14.3 months</t>
+          <t>Projected from FDA approval 2026-09-01 + 15.8 months</t>
         </is>
       </c>
     </row>
@@ -4409,14 +4406,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Targeting rapid launch post-approval</t>
+          <t>Targeting rapid launch post-approval. Source: Gilead Q4 2025 Earnings call.</t>
         </is>
       </c>
     </row>
@@ -4485,17 +4482,17 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>22 Nov 2027</t>
+          <t>29 May 2027</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>29 May 2028</t>
+          <t>19 Sep 2027</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>6 Dec 2028</t>
+          <t>10 Jan 2028</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -4510,7 +4507,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2026-07-18, HTA 2028-05-29)</t>
+          <t>UK SoC = max(guideline 2026-09-01, HTA 2027-09-19)</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4529,12 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>20 Jun 2027</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>11 Jun 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -4557,7 +4554,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2026-07-18, HTA 2027-06-11)</t>
+          <t>France SoC = max(guideline 2026-09-01, HTA 2027-07-26)</t>
         </is>
       </c>
     </row>
@@ -4579,17 +4576,17 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>18 Feb 2027</t>
+          <t>22 Nov 2026</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>3 Feb 2027</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>5 Apr 2027</t>
+          <t>17 Apr 2027</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -4604,7 +4601,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2026-07-18, EMA 2027-03-11). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-09-01, EMA 2027-02-03). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4623,12 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>29 Jul 2027</t>
+          <t>1 Nov 2027</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>16 Oct 2027</t>
+          <t>4 Dec 2027</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -4651,7 +4648,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2026-07-18, HTA 2027-10-16)</t>
+          <t>Italy SoC = max(guideline 2026-09-01, HTA 2027-12-04)</t>
         </is>
       </c>
     </row>
@@ -4673,12 +4670,12 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>25 Nov 2026</t>
+          <t>24 Feb 2027</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>26 Jul 2027</t>
+          <t>7 Sep 2027</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -4698,7 +4695,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2026-07-18, HTA 2027-07-26)</t>
+          <t>Spain SoC = max(guideline 2026-09-01, HTA 2027-09-07)</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4717,12 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>26 Jul 2027</t>
+          <t>26 Oct 2027</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>10 Nov 2027</t>
+          <t>25 Dec 2027</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -4745,7 +4742,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-11-10)</t>
+          <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-12-25)</t>
         </is>
       </c>
     </row>
@@ -4755,10 +4752,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4928,7 +4921,7 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>NEJM publication — 21 Jan 2026</t>
         </is>
@@ -4975,14 +4968,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Projected based on Gilead H2 2026 launch target</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>May come slightly after ASCENT-03 monotherapy approval</t>
+          <t>May come slightly after ASCENT-03 monotherapy approval.</t>
         </is>
       </c>
     </row>
@@ -5004,32 +4997,32 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>22 Dec 2026</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>10 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>5 May 2027</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+          <t>17 May 2027</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -5051,32 +5044,32 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>22 Dec 2026</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>10 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>5 May 2027</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+          <t>17 May 2027</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -5098,32 +5091,32 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>22 Dec 2026</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>10 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>5 May 2027</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+          <t>17 May 2027</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -5145,32 +5138,32 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>22 Dec 2026</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>10 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>5 May 2027</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+          <t>17 May 2027</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -5192,12 +5185,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>27 Jan 2027</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2 May 2027</t>
+          <t>4 Apr 2027</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -5205,19 +5198,19 @@
           <t>10 Jun 2027</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 7.0 months post-FDA</t>
+          <t>Analog-based projection (base): 6.1 months post-FDA</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 7.0 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 6.1 months</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5232,12 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>13 Apr 2027</t>
+          <t>14 Jul 2027</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>28 Aug 2027</t>
+          <t>13 Oct 2027</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -5252,19 +5245,19 @@
           <t>12 Jan 2028</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.4 months post-FDA</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 10.9 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 12.4 months</t>
         </is>
       </c>
     </row>
@@ -5304,14 +5297,14 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Initially Category 2A preferred; upgraded to Category 1 in v2.2026</t>
+          <t>Initially Category 2A preferred; upgraded to Category 1 in v2.2026. NCCN requires login at nccn.org.</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5344,7 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
@@ -5376,12 +5369,12 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -5389,19 +5382,19 @@
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5416,12 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -5436,19 +5429,19 @@
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -5470,12 +5463,12 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -5483,19 +5476,19 @@
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5510,12 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
@@ -5530,19 +5523,19 @@
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -5564,12 +5557,12 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>16 Dec 2025</t>
+          <t>18 Mar 2026</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>1 Oct 2026</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -5577,19 +5570,19 @@
           <t>13 Apr 2027</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -5611,32 +5604,32 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>22 Dec 2027</t>
+          <t>28 Jun 2027</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>28 Jun 2028</t>
+          <t>19 Oct 2027</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>5 Jan 2029</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+          <t>9 Feb 2028</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.6 months post-FDA</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 12.6 months</t>
         </is>
       </c>
     </row>
@@ -5658,12 +5651,12 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>29 Mar 2027</t>
+          <t>28 Jun 2027</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>23 Jul 2027</t>
+          <t>6 Sep 2027</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -5671,19 +5664,19 @@
           <t>12 Nov 2027</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+          <t>Analog-based projection (base): 11.2 months post-FDA</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 9.7 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 11.2 months</t>
         </is>
       </c>
     </row>
@@ -5705,12 +5698,12 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>19 Apr 2027</t>
+          <t>20 Jul 2027</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -5718,19 +5711,19 @@
           <t>1 Oct 2027</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 9.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5745,12 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>28 Aug 2027</t>
+          <t>1 Dec 2027</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>15 Nov 2027</t>
+          <t>3 Jan 2028</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -5765,19 +5758,19 @@
           <t>3 Feb 2028</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 13.5 months post-FDA</t>
+          <t>Analog-based projection (base): 15.1 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 13.5 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 15.1 months</t>
         </is>
       </c>
     </row>
@@ -5799,12 +5792,12 @@
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>25 Dec 2026</t>
+          <t>26 Mar 2027</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>25 Aug 2027</t>
+          <t>7 Oct 2027</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -5812,19 +5805,19 @@
           <t>22 Apr 2028</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.8 months post-FDA</t>
+          <t>Analog-based projection (base): 12.2 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 10.8 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 12.2 months</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5839,12 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>25 Aug 2027</t>
+          <t>25 Nov 2027</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>10 Dec 2027</t>
+          <t>24 Jan 2028</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -5859,19 +5852,19 @@
           <t>25 Mar 2028</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 14.3 months post-FDA</t>
+          <t>Analog-based projection (base): 15.8 months post-FDA</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-10-01 + 14.3 months</t>
+          <t>Projected from FDA approval 2026-10-01 + 15.8 months</t>
         </is>
       </c>
     </row>
@@ -5911,14 +5904,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Gilead guidance: accelerated launch H2 2026</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Combo launch may follow monotherapy by ~1 month</t>
+          <t>Combo launch may follow monotherapy by ~1 month. Source: Gilead Q4 2025 Earnings call.</t>
         </is>
       </c>
     </row>
@@ -5987,17 +5980,17 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>22 Dec 2027</t>
+          <t>28 Jun 2027</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>28 Jun 2028</t>
+          <t>19 Oct 2027</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>5 Jan 2029</t>
+          <t>9 Feb 2028</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -6012,7 +6005,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2026-08-17, HTA 2028-06-28)</t>
+          <t>UK SoC = max(guideline 2026-10-01, HTA 2027-10-19)</t>
         </is>
       </c>
     </row>
@@ -6034,12 +6027,12 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>19 Apr 2027</t>
+          <t>20 Jul 2027</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2027</t>
+          <t>25 Aug 2027</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -6059,7 +6052,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2026-08-17, HTA 2027-07-11)</t>
+          <t>France SoC = max(guideline 2026-10-01, HTA 2027-08-25)</t>
         </is>
       </c>
     </row>
@@ -6081,17 +6074,17 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>20 Mar 2027</t>
+          <t>22 Dec 2026</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>10 Apr 2027</t>
+          <t>5 Mar 2027</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>5 May 2027</t>
+          <t>17 May 2027</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -6106,7 +6099,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2026-08-17, EMA 2027-04-10). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-10-01, EMA 2027-03-05). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -6128,12 +6121,12 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>28 Aug 2027</t>
+          <t>1 Dec 2027</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>15 Nov 2027</t>
+          <t>3 Jan 2028</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -6153,7 +6146,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2026-08-17, HTA 2027-11-15)</t>
+          <t>Italy SoC = max(guideline 2026-10-01, HTA 2028-01-03)</t>
         </is>
       </c>
     </row>
@@ -6175,12 +6168,12 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>25 Dec 2026</t>
+          <t>26 Mar 2027</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>25 Aug 2027</t>
+          <t>7 Oct 2027</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -6200,7 +6193,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2026-08-17, HTA 2027-08-25)</t>
+          <t>Spain SoC = max(guideline 2026-10-01, HTA 2027-10-07)</t>
         </is>
       </c>
     </row>
@@ -6222,12 +6215,12 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>25 Aug 2027</t>
+          <t>25 Nov 2027</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>10 Dec 2027</t>
+          <t>24 Jan 2028</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -6247,7 +6240,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-12-10)</t>
+          <t>Canada SoC = max(guideline 2026-01-15, HTA 2028-01-24)</t>
         </is>
       </c>
     </row>
@@ -6257,11 +6250,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6379,19 +6367,19 @@
           <t>1 Mar 2025</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>ClinicalTrials.gov NCT05104866 (estimated)</t>
+          <t>ClinicalTrials.gov NCT05374512 — TROPION-Breast02</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>TROPION-Breast02 primary completion estimate</t>
+          <t>TROPION-Breast02 primary completion estimate. Note: NCT05104866 is TROPION-Breast01 (HR+/HER2-), not Breast02.</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6426,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Primary data supported sBLA submission</t>
+          <t>Primary data supported sBLA submission.</t>
         </is>
       </c>
     </row>
@@ -6478,14 +6466,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>PDUFA Q2 2026 under Priority Review</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Priority Review granted Feb 2026; PDUFA target date Q2 2026</t>
+          <t>Priority Review granted Feb 2026; PDUFA target date Q2 2026. Source: Daiichi Sankyo corporate communications.</t>
         </is>
       </c>
     </row>
@@ -6520,14 +6508,14 @@
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Daiichi Q3 FY2025 Earnings</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr"/>
@@ -6563,19 +6551,19 @@
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Based on regulatory submission accepted Dec 2025</t>
+          <t>Based on regulatory submission accepted Dec 2025. Source: Daiichi Sankyo Q3 FY2025 Earnings presentation.</t>
         </is>
       </c>
     </row>
@@ -6610,14 +6598,14 @@
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Daiichi Q3 FY2025 Earnings</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr"/>
@@ -6653,14 +6641,14 @@
           <t>1 Sep 2026</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Daiichi Q3 FY2025 Earnings</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>Daiichi Q3 FY2025 Earnings: EU approval projected Q3 2026</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr"/>
@@ -6683,12 +6671,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>18 Nov 2026</t>
+          <t>27 Sep 2026</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>31 Dec 2026</t>
+          <t>3 Dec 2026</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -6696,19 +6684,19 @@
           <t>8 Feb 2027</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 7.0 months post-FDA</t>
+          <t>Analog-based projection (base): 6.1 months post-FDA</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 7.0 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 6.1 months</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6718,12 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>12 Dec 2026</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>28 Apr 2027</t>
+          <t>13 Jun 2027</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -6743,19 +6731,19 @@
           <t>12 Sep 2027</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.4 months post-FDA</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 10.9 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 12.4 months</t>
         </is>
       </c>
     </row>
@@ -6795,14 +6783,14 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Category 2A other recommended; upgraded to Category 2A preferred in v2.2026</t>
+          <t>Category 2A other recommended; upgraded to Category 2A preferred in v2.2026. NCCN requires login at nccn.org.</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6830,7 @@
           <t>Known</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>NCCN Breast Cancer v1.2026</t>
         </is>
@@ -6867,12 +6855,12 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>16 Aug 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -6880,19 +6868,19 @@
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -6914,12 +6902,12 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>16 Aug 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -6927,19 +6915,19 @@
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6949,12 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>16 Aug 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -6974,19 +6962,19 @@
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -7008,12 +6996,12 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>16 Aug 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
@@ -7021,19 +7009,19 @@
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7043,12 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>16 Aug 2025</t>
+          <t>16 Nov 2025</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>17 Apr 2026</t>
+          <t>1 Jun 2026</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -7068,19 +7056,19 @@
           <t>12 Dec 2026</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -7102,32 +7090,32 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>22 Aug 2027</t>
+          <t>26 Feb 2027</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>27 Feb 2028</t>
+          <t>19 Jun 2027</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>5 Sep 2028</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+          <t>10 Oct 2027</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.6 months post-FDA</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 12.6 months</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7137,12 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>27 Nov 2026</t>
+          <t>26 Feb 2027</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>23 Mar 2027</t>
+          <t>7 May 2027</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -7162,19 +7150,19 @@
           <t>13 Jul 2027</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+          <t>Analog-based projection (base): 11.2 months post-FDA</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 9.7 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 11.2 months</t>
         </is>
       </c>
     </row>
@@ -7196,12 +7184,12 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>18 Dec 2026</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -7209,19 +7197,19 @@
           <t>1 Jun 2027</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 9.3 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -7243,12 +7231,12 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>28 Apr 2027</t>
+          <t>1 Aug 2027</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>16 Jul 2027</t>
+          <t>3 Sep 2027</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -7256,19 +7244,19 @@
           <t>4 Oct 2027</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 13.5 months post-FDA</t>
+          <t>Analog-based projection (base): 15.1 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 13.5 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 15.1 months</t>
         </is>
       </c>
     </row>
@@ -7290,12 +7278,12 @@
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>24 Nov 2026</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>25 Apr 2027</t>
+          <t>7 Jun 2027</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -7303,19 +7291,19 @@
           <t>22 Dec 2027</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.8 months post-FDA</t>
+          <t>Analog-based projection (base): 12.2 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 10.8 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 12.2 months</t>
         </is>
       </c>
     </row>
@@ -7337,12 +7325,12 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>25 Apr 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>10 Aug 2027</t>
+          <t>24 Sep 2027</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -7350,19 +7338,19 @@
           <t>24 Nov 2027</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 14.3 months post-FDA</t>
+          <t>Analog-based projection (base): 15.8 months post-FDA</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2026-06-01 + 14.3 months</t>
+          <t>Projected from FDA approval 2026-06-01 + 15.8 months</t>
         </is>
       </c>
     </row>
@@ -7402,14 +7390,14 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>Projected post-PDUFA</t>
         </is>
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>Expected rapid US launch following FDA approval</t>
+          <t>Expected rapid US launch following FDA approval. Source: Daiichi Sankyo corporate guidance.</t>
         </is>
       </c>
     </row>
@@ -7478,17 +7466,17 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>22 Aug 2027</t>
+          <t>26 Feb 2027</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>27 Feb 2028</t>
+          <t>19 Jun 2027</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>5 Sep 2028</t>
+          <t>10 Oct 2027</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -7503,7 +7491,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2026-04-17, HTA 2028-02-27)</t>
+          <t>UK SoC = max(guideline 2026-06-01, HTA 2027-06-19)</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7513,12 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>18 Dec 2026</t>
+          <t>20 Mar 2027</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>11 Mar 2027</t>
+          <t>25 Apr 2027</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -7550,7 +7538,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2026-04-17, HTA 2027-03-11)</t>
+          <t>France SoC = max(guideline 2026-06-01, HTA 2027-04-25)</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7585,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2026-04-17, EMA 2026-09-01). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2026-06-01, EMA 2026-09-01). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7607,12 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>28 Apr 2027</t>
+          <t>1 Aug 2027</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>16 Jul 2027</t>
+          <t>3 Sep 2027</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -7644,7 +7632,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2026-04-17, HTA 2027-07-16)</t>
+          <t>Italy SoC = max(guideline 2026-06-01, HTA 2027-09-03)</t>
         </is>
       </c>
     </row>
@@ -7666,12 +7654,12 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>24 Nov 2026</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>25 Apr 2027</t>
+          <t>7 Jun 2027</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -7691,7 +7679,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2026-04-17, HTA 2027-04-25)</t>
+          <t>Spain SoC = max(guideline 2026-06-01, HTA 2027-06-07)</t>
         </is>
       </c>
     </row>
@@ -7713,12 +7701,12 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>25 Apr 2027</t>
+          <t>26 Jul 2027</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>10 Aug 2027</t>
+          <t>24 Sep 2027</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -7738,7 +7726,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-08-10)</t>
+          <t>Canada SoC = max(guideline 2026-01-15, HTA 2027-09-24)</t>
         </is>
       </c>
     </row>
@@ -7748,14 +7736,6 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7932,7 +7912,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>Assumes data maturation + congress cycle</t>
+          <t>Assumes data maturation + congress cycle.</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7959,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Assumes standard or Priority Review</t>
+          <t>Assumes standard or Priority Review.</t>
         </is>
       </c>
     </row>
@@ -8001,32 +7981,32 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>24 Mar 2029</t>
         </is>
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2029</t>
+          <t>5 Jun 2029</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr">
         <is>
-          <t>5 Aug 2029</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="inlineStr">
+          <t>17 Aug 2029</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -8048,32 +8028,32 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>24 Mar 2029</t>
         </is>
       </c>
       <c r="E9" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2029</t>
+          <t>5 Jun 2029</t>
         </is>
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>5 Aug 2029</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+          <t>17 Aug 2029</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -8095,32 +8075,32 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>24 Mar 2029</t>
         </is>
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2029</t>
+          <t>5 Jun 2029</t>
         </is>
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>5 Aug 2029</t>
-        </is>
-      </c>
-      <c r="G10" s="11" t="inlineStr">
+          <t>17 Aug 2029</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -8142,32 +8122,32 @@
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>24 Mar 2029</t>
         </is>
       </c>
       <c r="E11" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2029</t>
+          <t>5 Jun 2029</t>
         </is>
       </c>
       <c r="F11" s="19" t="inlineStr">
         <is>
-          <t>5 Aug 2029</t>
-        </is>
-      </c>
-      <c r="G11" s="11" t="inlineStr">
+          <t>17 Aug 2029</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 6.3 months post-FDA</t>
+          <t>Analog-based projection (base): 5.1 months post-FDA</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 6.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 5.1 months</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8169,12 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>29 Apr 2029</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2 Aug 2029</t>
+          <t>5 Jul 2029</t>
         </is>
       </c>
       <c r="F12" s="19" t="inlineStr">
@@ -8202,19 +8182,19 @@
           <t>10 Sep 2029</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 7.0 months post-FDA</t>
+          <t>Analog-based projection (base): 6.1 months post-FDA</t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 7.0 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 6.1 months</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8216,12 @@
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>14 Jul 2029</t>
+          <t>14 Oct 2029</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>28 Nov 2029</t>
+          <t>13 Jan 2030</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
@@ -8249,19 +8229,19 @@
           <t>14 Apr 2030</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.4 months post-FDA</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 10.9 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 12.4 months</t>
         </is>
       </c>
     </row>
@@ -8288,27 +8268,27 @@
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>28 Jan 2029</t>
+          <t>15 Mar 2029</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
         <is>
-          <t>28 Jan 2029</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
+          <t>29 Apr 2029</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 0.9 months post-FDA</t>
+          <t>Analog-based projection (base): 2.4 months post-FDA</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 2.4 months</t>
         </is>
       </c>
     </row>
@@ -8335,27 +8315,27 @@
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>28 Jan 2029</t>
+          <t>15 Mar 2029</t>
         </is>
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>28 Jan 2029</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+          <t>29 Apr 2029</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 0.9 months post-FDA</t>
+          <t>Analog-based projection (base): 2.4 months post-FDA</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 0.9 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 2.4 months</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8357,12 @@
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>18 Mar 2028</t>
+          <t>18 Jun 2028</t>
         </is>
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>17 Nov 2028</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F16" s="19" t="inlineStr">
@@ -8390,19 +8370,19 @@
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -8424,12 +8404,12 @@
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>18 Mar 2028</t>
+          <t>18 Jun 2028</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>17 Nov 2028</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F17" s="19" t="inlineStr">
@@ -8437,19 +8417,19 @@
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8451,12 @@
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>18 Mar 2028</t>
+          <t>18 Jun 2028</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>17 Nov 2028</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F18" s="19" t="inlineStr">
@@ -8484,19 +8464,19 @@
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8498,12 @@
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>18 Mar 2028</t>
+          <t>18 Jun 2028</t>
         </is>
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>17 Nov 2028</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F19" s="19" t="inlineStr">
@@ -8531,19 +8511,19 @@
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8545,12 @@
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>18 Mar 2028</t>
+          <t>18 Jun 2028</t>
         </is>
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>17 Nov 2028</t>
+          <t>1 Jan 2029</t>
         </is>
       </c>
       <c r="F20" s="19" t="inlineStr">
@@ -8578,19 +8558,19 @@
           <t>14 Jul 2029</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): -1.5 months post-FDA</t>
+          <t>Analog-based projection (base): -0.0 months post-FDA</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + -1.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + -0.0 months</t>
         </is>
       </c>
     </row>
@@ -8612,32 +8592,32 @@
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>24 Mar 2030</t>
+          <t>28 Sep 2029</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>29 Sep 2030</t>
+          <t>19 Jan 2030</t>
         </is>
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>8 Apr 2031</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+          <t>12 May 2030</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 20.9 months post-FDA</t>
+          <t>Analog-based projection (base): 12.6 months post-FDA</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 20.9 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 12.6 months</t>
         </is>
       </c>
     </row>
@@ -8659,12 +8639,12 @@
       </c>
       <c r="D22" s="17" t="inlineStr">
         <is>
-          <t>29 Jun 2029</t>
+          <t>28 Sep 2029</t>
         </is>
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>23 Oct 2029</t>
+          <t>7 Dec 2029</t>
         </is>
       </c>
       <c r="F22" s="19" t="inlineStr">
@@ -8672,19 +8652,19 @@
           <t>12 Feb 2030</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.7 months post-FDA</t>
+          <t>Analog-based projection (base): 11.2 months post-FDA</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 9.7 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 11.2 months</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8686,12 @@
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>20 Jul 2029</t>
+          <t>20 Oct 2029</t>
         </is>
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>11 Oct 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="F23" s="19" t="inlineStr">
@@ -8719,19 +8699,19 @@
           <t>1 Jan 2030</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 9.3 months post-FDA</t>
+          <t>Analog-based projection (base): 10.8 months post-FDA</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 9.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 10.8 months</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8733,12 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>28 Nov 2029</t>
+          <t>3 Mar 2030</t>
         </is>
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>15 Feb 2030</t>
+          <t>5 Apr 2030</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -8766,19 +8746,19 @@
           <t>6 May 2030</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 13.5 months post-FDA</t>
+          <t>Analog-based projection (base): 15.1 months post-FDA</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 13.5 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 15.1 months</t>
         </is>
       </c>
     </row>
@@ -8800,12 +8780,12 @@
       </c>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>27 Mar 2029</t>
+          <t>26 Jun 2029</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>25 Nov 2029</t>
+          <t>7 Jan 2030</t>
         </is>
       </c>
       <c r="F25" s="19" t="inlineStr">
@@ -8813,19 +8793,19 @@
           <t>24 Jul 2030</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 10.8 months post-FDA</t>
+          <t>Analog-based projection (base): 12.2 months post-FDA</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 10.8 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 12.2 months</t>
         </is>
       </c>
     </row>
@@ -8847,12 +8827,12 @@
       </c>
       <c r="D26" s="17" t="inlineStr">
         <is>
-          <t>25 Nov 2029</t>
+          <t>25 Feb 2030</t>
         </is>
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>12 Mar 2030</t>
+          <t>26 Apr 2030</t>
         </is>
       </c>
       <c r="F26" s="19" t="inlineStr">
@@ -8860,19 +8840,19 @@
           <t>26 Jun 2030</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Analog-based projection (base): 14.3 months post-FDA</t>
+          <t>Analog-based projection (base): 15.8 months post-FDA</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>Projected from FDA approval 2029-01-01 + 14.3 months</t>
+          <t>Projected from FDA approval 2029-01-01 + 15.8 months</t>
         </is>
       </c>
     </row>
@@ -8942,12 +8922,12 @@
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>1 Feb 2029</t>
+          <t>15 Mar 2029</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
         <is>
-          <t>1 Feb 2029</t>
+          <t>29 Apr 2029</t>
         </is>
       </c>
       <c r="G28" s="19" t="inlineStr">
@@ -8962,7 +8942,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>US SoC = max(NCCN 2029-01-28, launch 2029-02-01)</t>
+          <t>US SoC = max(NCCN 2029-03-15, launch 2029-02-01)</t>
         </is>
       </c>
     </row>
@@ -8984,17 +8964,17 @@
       </c>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>24 Mar 2030</t>
+          <t>28 Sep 2029</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>29 Sep 2030</t>
+          <t>19 Jan 2030</t>
         </is>
       </c>
       <c r="F29" s="19" t="inlineStr">
         <is>
-          <t>8 Apr 2031</t>
+          <t>12 May 2030</t>
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
@@ -9009,7 +8989,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>UK SoC = max(guideline 2028-11-17, HTA 2030-09-29)</t>
+          <t>UK SoC = max(guideline 2029-01-01, HTA 2030-01-19)</t>
         </is>
       </c>
     </row>
@@ -9031,12 +9011,12 @@
       </c>
       <c r="D30" s="17" t="inlineStr">
         <is>
-          <t>20 Jul 2029</t>
+          <t>20 Oct 2029</t>
         </is>
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>11 Oct 2029</t>
+          <t>25 Nov 2029</t>
         </is>
       </c>
       <c r="F30" s="19" t="inlineStr">
@@ -9056,7 +9036,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>France SoC = max(guideline 2028-11-17, HTA 2029-10-11)</t>
+          <t>France SoC = max(guideline 2029-01-01, HTA 2029-11-25)</t>
         </is>
       </c>
     </row>
@@ -9078,17 +9058,17 @@
       </c>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>20 Jun 2029</t>
+          <t>24 Mar 2029</t>
         </is>
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>11 Jul 2029</t>
+          <t>5 Jun 2029</t>
         </is>
       </c>
       <c r="F31" s="19" t="inlineStr">
         <is>
-          <t>5 Aug 2029</t>
+          <t>17 Aug 2029</t>
         </is>
       </c>
       <c r="G31" s="19" t="inlineStr">
@@ -9103,7 +9083,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>DE SoC = max(ESMO 2028-11-17, EMA 2029-07-11). G-BA does not gate access.</t>
+          <t>DE SoC = max(ESMO 2029-01-01, EMA 2029-06-05). G-BA does not gate access.</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9105,12 @@
       </c>
       <c r="D32" s="17" t="inlineStr">
         <is>
-          <t>28 Nov 2029</t>
+          <t>3 Mar 2030</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>15 Feb 2030</t>
+          <t>5 Apr 2030</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -9150,7 +9130,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>Italy SoC = max(guideline 2028-11-17, HTA 2030-02-15)</t>
+          <t>Italy SoC = max(guideline 2029-01-01, HTA 2030-04-05)</t>
         </is>
       </c>
     </row>
@@ -9172,12 +9152,12 @@
       </c>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>27 Mar 2029</t>
+          <t>26 Jun 2029</t>
         </is>
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>25 Nov 2029</t>
+          <t>7 Jan 2030</t>
         </is>
       </c>
       <c r="F33" s="19" t="inlineStr">
@@ -9197,7 +9177,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>Spain SoC = max(guideline 2028-11-17, HTA 2029-11-25)</t>
+          <t>Spain SoC = max(guideline 2029-01-01, HTA 2030-01-07)</t>
         </is>
       </c>
     </row>
@@ -9219,12 +9199,12 @@
       </c>
       <c r="D34" s="17" t="inlineStr">
         <is>
-          <t>25 Nov 2029</t>
+          <t>25 Feb 2030</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>12 Mar 2030</t>
+          <t>26 Apr 2030</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -9244,7 +9224,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>Canada SoC = max(guideline 2029-01-28, HTA 2030-03-12)</t>
+          <t>Canada SoC = max(guideline 2029-03-15, HTA 2030-04-26)</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10611,7 @@
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>Extended (34mo) — flexible timing</t>
+          <t>Extended (35mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10648,42 +10628,42 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>Extended (25mo) — flexible timing</t>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Moderate (17mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Q2 2028</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>Extended (26mo) — flexible timing</t>
+          <t>Q4 2027</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Moderate (18mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Q1 2028</t>
+          <t>Q2 2027</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>Moderate (22mo) — plan enrollment</t>
+          <t>Moderate (14mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Q3 2030</t>
+          <t>Q1 2030</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t>Extended (53mo) — flexible timing</t>
+          <t>Extended (45mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10700,32 +10680,32 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Moderate (15mo) — plan enrollment</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Q3 2027</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Moderate (16mo) — plan enrollment</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Moderate (14mo) — plan enrollment</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Q3 2027</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t>Moderate (15mo) — plan enrollment</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Q1 2027</t>
-        </is>
-      </c>
       <c r="H7" s="23" t="inlineStr">
         <is>
-          <t>Narrow (11mo) — prioritize now</t>
+          <t>Narrow (12mo) — prioritize now</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -10735,7 +10715,7 @@
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>Extended (42mo) — flexible timing</t>
+          <t>Extended (43mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10757,19 +10737,19 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
+          <t>Narrow (10mo) — prioritize now</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Q1 2027</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
           <t>Narrow (11mo) — prioritize now</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Q2 2027</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Narrow (12mo) — prioritize now</t>
-        </is>
-      </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Q3 2026</t>
@@ -10782,12 +10762,12 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Q3 2029</t>
+          <t>Q2 2029</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>Extended (39mo) — flexible timing</t>
+          <t>Extended (38mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10809,17 +10789,17 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Moderate (18mo) — plan enrollment</t>
+          <t>Moderate (20mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Moderate (19mo) — plan enrollment</t>
+          <t>Moderate (21mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -10829,17 +10809,17 @@
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>Moderate (15mo) — plan enrollment</t>
+          <t>Moderate (17mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Q1 2030</t>
+          <t>Q2 2030</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>Extended (46mo) — flexible timing</t>
+          <t>Extended (48mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10861,17 +10841,17 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>Moderate (15mo) — plan enrollment</t>
+          <t>Moderate (17mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Q3 2027</t>
+          <t>Q4 2027</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Moderate (16mo) — plan enrollment</t>
+          <t>Moderate (18mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -10879,19 +10859,19 @@
           <t>Q2 2027</t>
         </is>
       </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>Narrow (12mo) — prioritize now</t>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>Moderate (14mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Q4 2029</t>
+          <t>Q1 2030</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t>Extended (43mo) — flexible timing</t>
+          <t>Extended (45mo) — flexible timing</t>
         </is>
       </c>
     </row>
@@ -10913,17 +10893,17 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>Moderate (19mo) — plan enrollment</t>
+          <t>Moderate (20mo) — plan enrollment</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Q4 2027</t>
+          <t>Q1 2028</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Moderate (20mo) — plan enrollment</t>
+          <t>Moderate (21mo) — plan enrollment</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -10933,17 +10913,17 @@
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>Moderate (16mo) — plan enrollment</t>
+          <t>Moderate (17mo) — plan enrollment</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Q1 2030</t>
+          <t>Q2 2030</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>Extended (47mo) — flexible timing</t>
+          <t>Extended (48mo) — flexible timing</t>
         </is>
       </c>
     </row>
